--- a/舞曲排布_示例.xlsx
+++ b/舞曲排布_示例.xlsx
@@ -5,17 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jerome\Ballroom-Dance-Audio-Pipeline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jerome\Ballroom-Dance-Audio-Pipeline-backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B256CF73-B22C-456F-B52E-EBADF5BFBD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B398AB1-0CD1-4186-8347-9080761987A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{DF957FAE-4702-483C-9138-4CF31EE165DE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{DF957FAE-4702-483C-9138-4CF31EE165DE}"/>
   </bookViews>
   <sheets>
     <sheet name="舞种配比" sheetId="2" r:id="rId1"/>
     <sheet name="完整曲序" sheetId="3" r:id="rId2"/>
     <sheet name="排列检查" sheetId="5" r:id="rId3"/>
+    <sheet name="排布结果" sheetId="7" r:id="rId4"/>
+    <sheet name="生成条件" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -94,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="209">
   <si>
     <t>大类</t>
   </si>
@@ -1299,6 +1301,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>第一首和最后一首必须为摩登舞-华尔兹（慢）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.每首平均按三分钟计算，两个半小时限排50首。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>三步踩</t>
   </si>
   <si>
@@ -1359,11 +1369,23 @@
     <t>周舞</t>
   </si>
   <si>
-    <t>第一首和最后一首必须为摩登舞-华尔兹（慢）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.每首平均按三分钟计算，两个半小时限排50首。</t>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件记录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3237,7 +3259,7 @@
       </c>
       <c r="D21" s="37">
         <f>COUNTIF(完整曲序!$C$2:$C$105,$B21)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="38" t="s">
         <v>88</v>
@@ -4264,7 +4286,7 @@
         <v>中</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F18" s="62"/>
       <c r="G18" s="74">
@@ -4303,7 +4325,7 @@
         <v>中</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F19" s="62"/>
       <c r="G19" s="74">
@@ -4342,7 +4364,7 @@
         <v>中</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="74">
@@ -4381,7 +4403,7 @@
         <v>中</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="74">
@@ -4420,7 +4442,7 @@
         <v>慢</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F22" s="62"/>
       <c r="G22" s="74">
@@ -4459,7 +4481,7 @@
         <v>慢</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F23" s="62"/>
       <c r="G23" s="74">
@@ -4498,7 +4520,7 @@
         <v>慢</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F24" s="62"/>
       <c r="G24" s="74">
@@ -4537,7 +4559,7 @@
         <v>慢</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F25" s="62"/>
       <c r="G25" s="74">
@@ -4576,7 +4598,7 @@
         <v>慢</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F26" s="62"/>
       <c r="G26" s="74">
@@ -4615,7 +4637,7 @@
         <v>慢</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F27" s="62"/>
       <c r="G27" s="74">
@@ -4654,7 +4676,7 @@
         <v>中</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F28" s="62"/>
       <c r="G28" s="74">
@@ -4693,7 +4715,7 @@
         <v>中</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F29" s="62"/>
       <c r="G29" s="74">
@@ -4732,7 +4754,7 @@
         <v>中</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F30" s="62"/>
       <c r="G30" s="74">
@@ -4771,7 +4793,7 @@
         <v>中</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F31" s="62"/>
       <c r="G31" s="74">
@@ -4810,7 +4832,7 @@
         <v>快</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F32" s="62"/>
       <c r="G32" s="74">
@@ -4849,7 +4871,7 @@
         <v>中</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F33" s="62"/>
       <c r="G33" s="74">
@@ -4888,7 +4910,7 @@
         <v>中</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F34" s="62"/>
       <c r="G34" s="74">
@@ -4927,7 +4949,7 @@
         <v>慢</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F35" s="62"/>
       <c r="G35" s="74">
@@ -4959,14 +4981,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E36)), _xlpm.keywords, "")
 )</f>
-        <v>中三</v>
+        <v>休闲伦巴</v>
       </c>
       <c r="D36" s="5" t="str">
         <f>_xlfn.XLOOKUP($C36,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
-        <v>中</v>
+        <v>慢</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F36" s="62"/>
       <c r="G36" s="74">
@@ -4998,14 +5020,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E37)), _xlpm.keywords, "")
 )</f>
-        <v>中四</v>
+        <v>中三</v>
       </c>
       <c r="D37" s="11" t="str">
         <f>_xlfn.XLOOKUP($C37,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>中</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F37" s="62"/>
       <c r="G37" s="74">
@@ -5037,14 +5059,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E38)), _xlpm.keywords, "")
 )</f>
-        <v>快四</v>
+        <v>中四</v>
       </c>
       <c r="D38" s="5" t="str">
         <f>_xlfn.XLOOKUP($C38,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
-        <v>快</v>
+        <v>中</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F38" s="62"/>
       <c r="G38" s="74">
@@ -5069,21 +5091,21 @@
       </c>
       <c r="B39" s="4" t="str">
         <f>_xlfn.XLOOKUP($C39,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
-        <v>集体舞</v>
+        <v>交谊舞</v>
       </c>
       <c r="C39" s="15" t="str" cm="1">
         <f t="array" ref="C39">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E39)), _xlpm.keywords, "")
 )</f>
-        <v>兔子舞</v>
+        <v>快四</v>
       </c>
       <c r="D39" s="5" t="str">
         <f>_xlfn.XLOOKUP($C39,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
-        <v>中</v>
+        <v>快</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F39" s="62"/>
       <c r="G39" s="74">
@@ -5115,14 +5137,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E40)), _xlpm.keywords, "")
 )</f>
-        <v>十六步</v>
+        <v>兔子舞</v>
       </c>
       <c r="D40" s="5" t="str">
         <f>_xlfn.XLOOKUP($C40,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>中</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F40" s="62"/>
       <c r="G40" s="74">
@@ -5154,14 +5176,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E41)), _xlpm.keywords, "")
 )</f>
-        <v>三十二步</v>
+        <v>十六步</v>
       </c>
       <c r="D41" s="8" t="str">
         <f>_xlfn.XLOOKUP($C41,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>中</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F41" s="62"/>
       <c r="G41" s="74">
@@ -5193,14 +5215,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E42)), _xlpm.keywords, "")
 )</f>
-        <v>DJ</v>
+        <v>三十二步</v>
       </c>
       <c r="D42" s="5" t="str">
         <f>_xlfn.XLOOKUP($C42,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>中</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F42" s="62"/>
       <c r="G42" s="74">
@@ -5225,21 +5247,21 @@
       </c>
       <c r="B43" s="4" t="str">
         <f>_xlfn.XLOOKUP($C43,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
-        <v>网红舞</v>
+        <v>集体舞</v>
       </c>
       <c r="C43" s="15" t="str" cm="1">
         <f t="array" ref="C43">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E43)), _xlpm.keywords, "")
 )</f>
-        <v>汉舞</v>
+        <v>DJ</v>
       </c>
       <c r="D43" s="5" t="str">
         <f>_xlfn.XLOOKUP($C43,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
-        <v>慢</v>
+        <v>中</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F43" s="62"/>
       <c r="G43" s="74">
@@ -5271,14 +5293,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E44)), _xlpm.keywords, "")
 )</f>
-        <v>唐舞</v>
+        <v>汉舞</v>
       </c>
       <c r="D44" s="7" t="str">
         <f>_xlfn.XLOOKUP($C44,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>慢</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F44" s="62"/>
       <c r="G44" s="74">
@@ -5310,14 +5332,14 @@
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E45)), _xlpm.keywords, "")
 )</f>
-        <v>周舞</v>
+        <v>唐舞</v>
       </c>
       <c r="D45" s="7" t="str">
         <f>_xlfn.XLOOKUP($C45,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>慢</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F45" s="62"/>
       <c r="G45" s="74">
@@ -5342,20 +5364,22 @@
       </c>
       <c r="B46" s="4" t="str">
         <f>_xlfn.XLOOKUP($C46,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
-        <v/>
+        <v>网红舞</v>
       </c>
       <c r="C46" s="15" t="str" cm="1">
         <f t="array" ref="C46">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E46)), _xlpm.keywords, "")
 )</f>
-        <v/>
+        <v>周舞</v>
       </c>
       <c r="D46" s="5" t="str">
         <f>_xlfn.XLOOKUP($C46,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="4"/>
+        <v>慢</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>203</v>
+      </c>
       <c r="F46" s="62"/>
       <c r="G46" s="74">
         <v>0</v>
@@ -5607,8 +5631,8 @@
         <v>0</v>
       </c>
       <c r="G53" s="69">
-        <f>COUNTA(E:E)-2</f>
-        <v>43</v>
+        <f>COUNTA(E:E)-1</f>
+        <v>45</v>
       </c>
       <c r="H53" s="70" t="str" cm="1">
         <f t="array" ref="H53">_xlfn.LET(
@@ -5847,7 +5871,7 @@
         <f>舞种配比!B2</f>
         <v>华尔兹</v>
       </c>
-      <c r="W2" s="6">
+      <c r="W2" s="79">
         <v>3</v>
       </c>
       <c r="X2" t="str">
@@ -5921,7 +5945,7 @@
         <f>舞种配比!B3</f>
         <v>维也纳华尔兹</v>
       </c>
-      <c r="W3" s="6">
+      <c r="W3" s="79">
         <v>2</v>
       </c>
       <c r="X3" t="str">
@@ -6002,7 +6026,7 @@
         <f>舞种配比!B4</f>
         <v>探戈</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="79">
         <v>1</v>
       </c>
       <c r="X4" t="str">
@@ -6063,7 +6087,7 @@
         <f>舞种配比!B5</f>
         <v>狐步</v>
       </c>
-      <c r="W5" s="6">
+      <c r="W5" s="79">
         <v>1</v>
       </c>
       <c r="X5" t="str">
@@ -6124,7 +6148,7 @@
         <f>舞种配比!B6</f>
         <v>快步</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="79">
         <v>1</v>
       </c>
       <c r="X6" t="str">
@@ -6172,7 +6196,7 @@
         <f>舞种配比!B7</f>
         <v>伦巴</v>
       </c>
-      <c r="W7" s="6">
+      <c r="W7" s="79">
         <v>3</v>
       </c>
       <c r="X7" t="str">
@@ -6253,7 +6277,7 @@
         <f>舞种配比!B8</f>
         <v>恰恰</v>
       </c>
-      <c r="W8" s="6">
+      <c r="W8" s="79">
         <v>2</v>
       </c>
       <c r="X8" t="str">
@@ -6307,7 +6331,7 @@
         <f>舞种配比!B9</f>
         <v>桑巴</v>
       </c>
-      <c r="W9" s="6">
+      <c r="W9" s="79">
         <v>1</v>
       </c>
       <c r="X9" t="str">
@@ -6361,7 +6385,7 @@
         <f>舞种配比!B10</f>
         <v>牛仔</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W10" s="79">
         <v>1</v>
       </c>
       <c r="X10" t="str">
@@ -6408,7 +6432,7 @@
         <f>舞种配比!B11</f>
         <v>斗牛</v>
       </c>
-      <c r="W11" s="6">
+      <c r="W11" s="79">
         <v>1</v>
       </c>
       <c r="X11" t="str">
@@ -6455,7 +6479,7 @@
         <f>舞种配比!B12</f>
         <v>三步踩</v>
       </c>
-      <c r="W12" s="6">
+      <c r="W12" s="79">
         <v>2</v>
       </c>
       <c r="X12" t="str">
@@ -6502,7 +6526,7 @@
         <f>舞种配比!B13</f>
         <v>平四</v>
       </c>
-      <c r="W13" s="6">
+      <c r="W13" s="79">
         <v>2</v>
       </c>
       <c r="X13" t="str">
@@ -6552,7 +6576,7 @@
         <f>舞种配比!B14</f>
         <v>慢三</v>
       </c>
-      <c r="W14" s="6">
+      <c r="W14" s="79">
         <v>3</v>
       </c>
       <c r="X14" t="str">
@@ -6596,13 +6620,13 @@
       </c>
       <c r="I15" s="96"/>
       <c r="K15" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="V15" s="107" t="str">
         <f>舞种配比!B15</f>
         <v>慢四</v>
       </c>
-      <c r="W15" s="6">
+      <c r="W15" s="79">
         <v>3</v>
       </c>
       <c r="X15" t="str">
@@ -6652,7 +6676,7 @@
         <f>舞种配比!B16</f>
         <v>并四</v>
       </c>
-      <c r="W16" s="6">
+      <c r="W16" s="79">
         <v>3</v>
       </c>
       <c r="X16" t="str">
@@ -6696,13 +6720,13 @@
       </c>
       <c r="I17" s="96"/>
       <c r="K17" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="V17" s="107" t="str">
         <f>舞种配比!B17</f>
         <v>水兵舞</v>
       </c>
-      <c r="W17" s="6">
+      <c r="W17" s="79">
         <v>1</v>
       </c>
       <c r="X17" t="str">
@@ -6752,7 +6776,7 @@
         <f>舞种配比!B18</f>
         <v>鬼步舞</v>
       </c>
-      <c r="W18" s="6">
+      <c r="W18" s="79">
         <v>1</v>
       </c>
       <c r="X18" t="str">
@@ -6802,7 +6826,7 @@
         <f>舞种配比!B19</f>
         <v>吉特巴</v>
       </c>
-      <c r="W19" s="6">
+      <c r="W19" s="79">
         <v>1</v>
       </c>
       <c r="X19" t="str">
@@ -6852,7 +6876,7 @@
         <f>舞种配比!B20</f>
         <v>点帕斯</v>
       </c>
-      <c r="W20" s="6">
+      <c r="W20" s="79">
         <v>1</v>
       </c>
       <c r="X20" t="str">
@@ -6902,8 +6926,8 @@
         <f>舞种配比!B21</f>
         <v>休闲伦巴</v>
       </c>
-      <c r="W21" s="6">
-        <v>1</v>
+      <c r="W21" s="79">
+        <v>2</v>
       </c>
       <c r="X21" t="str">
         <f t="shared" si="4"/>
@@ -6952,7 +6976,7 @@
         <f>舞种配比!B22</f>
         <v>中三</v>
       </c>
-      <c r="W22" s="6">
+      <c r="W22" s="79">
         <v>1</v>
       </c>
       <c r="X22" t="str">
@@ -6961,7 +6985,7 @@
       </c>
       <c r="Y22">
         <f t="shared" si="7"/>
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7002,7 +7026,7 @@
         <f>舞种配比!B23</f>
         <v>中四</v>
       </c>
-      <c r="W23" s="6">
+      <c r="W23" s="79">
         <v>1</v>
       </c>
       <c r="X23" t="str">
@@ -7011,7 +7035,7 @@
       </c>
       <c r="Y23">
         <f t="shared" si="7"/>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7052,7 +7076,7 @@
         <f>舞种配比!B24</f>
         <v>快四</v>
       </c>
-      <c r="W24" s="6">
+      <c r="W24" s="79">
         <v>1</v>
       </c>
       <c r="X24" t="str">
@@ -7061,7 +7085,7 @@
       </c>
       <c r="Y24">
         <f t="shared" si="7"/>
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7102,7 +7126,7 @@
         <f>舞种配比!B25</f>
         <v>兔子舞</v>
       </c>
-      <c r="W25" s="6">
+      <c r="W25" s="79">
         <v>1</v>
       </c>
       <c r="X25" t="str">
@@ -7111,7 +7135,7 @@
       </c>
       <c r="Y25">
         <f t="shared" si="7"/>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7152,7 +7176,7 @@
         <f>舞种配比!B26</f>
         <v>十六步</v>
       </c>
-      <c r="W26" s="6">
+      <c r="W26" s="79">
         <v>1</v>
       </c>
       <c r="X26" t="str">
@@ -7161,7 +7185,7 @@
       </c>
       <c r="Y26">
         <f t="shared" si="7"/>
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7202,7 +7226,7 @@
         <f>舞种配比!B27</f>
         <v>三十二步</v>
       </c>
-      <c r="W27" s="6">
+      <c r="W27" s="79">
         <v>1</v>
       </c>
       <c r="X27" t="str">
@@ -7211,7 +7235,7 @@
       </c>
       <c r="Y27">
         <f t="shared" si="7"/>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7252,7 +7276,7 @@
         <f>舞种配比!B28</f>
         <v>DJ</v>
       </c>
-      <c r="W28" s="6">
+      <c r="W28" s="79">
         <v>1</v>
       </c>
       <c r="X28" t="str">
@@ -7261,7 +7285,7 @@
       </c>
       <c r="Y28">
         <f t="shared" si="7"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7302,7 +7326,7 @@
         <f>舞种配比!B29</f>
         <v>汉舞</v>
       </c>
-      <c r="W29" s="6">
+      <c r="W29" s="79">
         <v>1</v>
       </c>
       <c r="X29" t="str">
@@ -7311,7 +7335,7 @@
       </c>
       <c r="Y29">
         <f t="shared" si="7"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7352,7 +7376,7 @@
         <f>舞种配比!B30</f>
         <v>唐舞</v>
       </c>
-      <c r="W30" s="6">
+      <c r="W30" s="79">
         <v>1</v>
       </c>
       <c r="X30" t="str">
@@ -7361,7 +7385,7 @@
       </c>
       <c r="Y30">
         <f t="shared" si="7"/>
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7402,7 +7426,7 @@
         <f>舞种配比!B31</f>
         <v>周舞</v>
       </c>
-      <c r="W31" s="6">
+      <c r="W31" s="79">
         <v>1</v>
       </c>
       <c r="X31" t="str">
@@ -7411,7 +7435,7 @@
       </c>
       <c r="Y31">
         <f t="shared" si="7"/>
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7452,13 +7476,14 @@
         <f>舞种配比!B32</f>
         <v>0</v>
       </c>
+      <c r="W32" s="79"/>
       <c r="X32" t="str">
         <f t="shared" si="4"/>
         <v>鬼步舞</v>
       </c>
       <c r="Y32">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7499,13 +7524,14 @@
         <f>舞种配比!B33</f>
         <v>0</v>
       </c>
+      <c r="W33" s="79"/>
       <c r="X33" t="str">
         <f t="shared" si="4"/>
         <v>吉特巴</v>
       </c>
       <c r="Y33">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7546,13 +7572,14 @@
         <f>舞种配比!B34</f>
         <v>0</v>
       </c>
+      <c r="W34" s="79"/>
       <c r="X34" t="str">
         <f t="shared" si="4"/>
         <v>点帕斯</v>
       </c>
       <c r="Y34">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7593,13 +7620,14 @@
         <f>舞种配比!B35</f>
         <v>0</v>
       </c>
+      <c r="W35" s="79"/>
       <c r="X35" t="str">
         <f t="shared" si="4"/>
         <v>休闲伦巴</v>
       </c>
       <c r="Y35">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7637,13 +7665,14 @@
         <f>舞种配比!B36</f>
         <v>0</v>
       </c>
+      <c r="W36" s="79"/>
       <c r="X36" t="str">
         <f t="shared" si="4"/>
-        <v>中三</v>
+        <v>休闲伦巴</v>
       </c>
       <c r="Y36">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7681,13 +7710,14 @@
         <f>舞种配比!B37</f>
         <v>0</v>
       </c>
+      <c r="W37" s="79"/>
       <c r="X37" t="str">
         <f t="shared" si="4"/>
-        <v>中四</v>
+        <v>中三</v>
       </c>
       <c r="Y37">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7725,13 +7755,14 @@
         <f>舞种配比!B38</f>
         <v>0</v>
       </c>
+      <c r="W38" s="79"/>
       <c r="X38" t="str">
         <f t="shared" si="4"/>
-        <v>快四</v>
+        <v>中四</v>
       </c>
       <c r="Y38">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7769,13 +7800,14 @@
         <f>舞种配比!B39</f>
         <v>0</v>
       </c>
+      <c r="W39" s="79"/>
       <c r="X39" t="str">
         <f t="shared" si="4"/>
-        <v>兔子舞</v>
+        <v>快四</v>
       </c>
       <c r="Y39">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7813,13 +7845,14 @@
         <f>舞种配比!B40</f>
         <v>0</v>
       </c>
+      <c r="W40" s="79"/>
       <c r="X40" t="str">
         <f t="shared" si="4"/>
-        <v>十六步</v>
+        <v>兔子舞</v>
       </c>
       <c r="Y40">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7857,13 +7890,14 @@
         <f>舞种配比!B41</f>
         <v>0</v>
       </c>
+      <c r="W41" s="79"/>
       <c r="X41" t="str">
         <f t="shared" si="4"/>
-        <v>三十二步</v>
+        <v>十六步</v>
       </c>
       <c r="Y41">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7901,13 +7935,14 @@
         <f>舞种配比!B42</f>
         <v>0</v>
       </c>
+      <c r="W42" s="79"/>
       <c r="X42" t="str">
         <f t="shared" si="4"/>
-        <v>DJ</v>
+        <v>三十二步</v>
       </c>
       <c r="Y42">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7945,13 +7980,14 @@
         <f>舞种配比!B43</f>
         <v>0</v>
       </c>
+      <c r="W43" s="79"/>
       <c r="X43" t="str">
         <f t="shared" si="4"/>
-        <v>汉舞</v>
+        <v>DJ</v>
       </c>
       <c r="Y43">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -7989,13 +8025,14 @@
         <f>舞种配比!B44</f>
         <v>0</v>
       </c>
+      <c r="W44" s="79"/>
       <c r="X44" t="str">
         <f t="shared" si="4"/>
-        <v>唐舞</v>
+        <v>汉舞</v>
       </c>
       <c r="Y44">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8033,13 +8070,14 @@
         <f>舞种配比!B45</f>
         <v>0</v>
       </c>
+      <c r="W45" s="79"/>
       <c r="X45" t="str">
         <f t="shared" si="4"/>
-        <v>周舞</v>
+        <v>唐舞</v>
       </c>
       <c r="Y45">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8077,13 +8115,14 @@
         <f>舞种配比!B46</f>
         <v>0</v>
       </c>
+      <c r="W46" s="79"/>
       <c r="X46" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>周舞</v>
       </c>
       <c r="Y46">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8121,13 +8160,14 @@
         <f>舞种配比!B47</f>
         <v>0</v>
       </c>
+      <c r="W47" s="79"/>
       <c r="X47" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Y47">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8165,13 +8205,14 @@
         <f>舞种配比!B48</f>
         <v>0</v>
       </c>
+      <c r="W48" s="79"/>
       <c r="X48" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Y48">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8209,13 +8250,14 @@
         <f>舞种配比!B49</f>
         <v>0</v>
       </c>
+      <c r="W49" s="79"/>
       <c r="X49" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Y49">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8253,13 +8295,14 @@
         <f>舞种配比!B50</f>
         <v>0</v>
       </c>
+      <c r="W50" s="79"/>
       <c r="X50" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Y50">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8297,13 +8340,14 @@
         <f>舞种配比!B51</f>
         <v>0</v>
       </c>
+      <c r="W51" s="79"/>
       <c r="X51" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Y51">
         <f t="shared" si="7"/>
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -8434,4 +8478,48 @@
     </ext>
   </extLst>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFEC3996-80B8-44F0-BEE4-B839E9989208}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB16A34D-A06D-4D2F-B79C-33D23635D23F}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/舞曲排布_示例.xlsx
+++ b/舞曲排布_示例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jerome\git\Ballroom-Dance-Audio-Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51381B19-1971-4045-955F-003E94DCBE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1541715-0389-4491-80FF-3041D0E00770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,12 +196,15 @@
     <t>A:标题 + 艺术家 + 专辑；B:320k CBR 并发2；C:淡入0.1s 淡出5.0s；D:时长8s 音量0.2 位置middle</t>
   </si>
   <si>
+    <t>08月15日00时54分</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
     <t>无固定位置</t>
   </si>
   <si>
-    <t>08月15日00时54分</t>
-  </si>
-  <si>
     <t>间隔6首</t>
   </si>
   <si>
@@ -728,10 +731,6 @@
   </si>
   <si>
     <t>终总时长</t>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2050,700 +2049,700 @@
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" s="108">
         <v>3</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H2" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="108">
         <v>2</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H3" s="23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="108">
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="18"/>
       <c r="G4" s="22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H4" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="108">
         <v>1</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" s="108">
         <v>1</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="109">
         <v>4</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="26"/>
       <c r="G7" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" s="109">
         <v>3</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I8" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" s="109">
         <v>2</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" s="26"/>
       <c r="G9" s="27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I9" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="109">
         <v>1</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" s="26"/>
       <c r="G10" s="27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I10" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D11" s="109">
         <v>1</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I11" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9" s="36" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D12" s="110">
         <v>2</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I12" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:9" s="36" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" s="110">
         <v>2</v>
       </c>
       <c r="E13" s="32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I13" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" s="111">
         <v>3</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14" s="40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I14" s="42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D15" s="111">
         <v>3</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G15" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I15" s="42" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D16" s="111">
         <v>1</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G16" s="40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" s="42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I16" s="42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" s="111">
         <v>1</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G17" s="40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H17" s="42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" s="111">
         <v>1</v>
       </c>
       <c r="E18" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G18" s="40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H18" s="42" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D19" s="111">
         <v>1</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G19" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H19" s="42" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D20" s="111">
         <v>1</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F20" s="39" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G20" s="40" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="111">
         <v>1</v>
       </c>
       <c r="E21" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G21" s="40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H21" s="42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D22" s="111">
         <v>1</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22" s="39"/>
       <c r="G22" s="37"/>
       <c r="H22" s="45"/>
       <c r="I22" s="42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23" s="111">
         <v>1</v>
       </c>
       <c r="E23" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F23" s="39"/>
       <c r="G23" s="37"/>
       <c r="H23" s="45"/>
       <c r="I23" s="42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="111">
         <v>1</v>
       </c>
       <c r="E24" s="38" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F24" s="39"/>
       <c r="G24" s="37"/>
       <c r="H24" s="45"/>
       <c r="I24" s="42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D25" s="112">
         <v>1</v>
       </c>
       <c r="E25" s="47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G25" s="49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H25" s="50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I25" s="51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" s="46" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C26" s="46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D26" s="112">
         <v>1</v>
@@ -2753,47 +2752,47 @@
       <c r="G26" s="46"/>
       <c r="H26" s="53"/>
       <c r="I26" s="51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" s="46" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C27" s="46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="112">
         <v>1</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G27" s="46" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="112">
         <v>1</v>
@@ -2802,79 +2801,79 @@
       <c r="F28" s="48"/>
       <c r="G28" s="46"/>
       <c r="H28" s="50" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I28" s="51" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="60" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B29" s="54" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C29" s="54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" s="113">
         <v>1</v>
       </c>
       <c r="E29" s="56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F29" s="57" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G29" s="58" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H29" s="59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I29" s="59" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="60" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B30" s="54" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D30" s="113">
         <v>1</v>
       </c>
       <c r="E30" s="56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F30" s="58"/>
       <c r="G30" s="55"/>
       <c r="H30" s="61"/>
       <c r="I30" s="59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="60" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="54" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B31" s="54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C31" s="54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D31" s="113">
         <v>1</v>
       </c>
       <c r="E31" s="56" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F31" s="58"/>
       <c r="G31" s="55"/>
@@ -2883,7 +2882,7 @@
     </row>
     <row r="32" spans="1:9" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -2892,11 +2891,11 @@
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I32" s="12"/>
     </row>
@@ -2980,7 +2979,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.19921875" style="6" bestFit="1" customWidth="1"/>
@@ -3040,22 +3039,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
@@ -3068,7 +3067,6 @@
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
-      <c r="F5"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6"/>
@@ -3079,6 +3077,9 @@
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8"/>
@@ -3103,14 +3104,6 @@
       <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3129,362 +3122,362 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3509,60 +3502,60 @@
   <sheetData>
     <row r="1" spans="1:20" s="103" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="97" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="98" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="98" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="99" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F1" s="99" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="99" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H1" s="99" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I1" s="99" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J1" s="100"/>
       <c r="K1" s="101" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L1" s="100" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M1" s="100"/>
       <c r="N1" s="101" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O1" s="100" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P1" s="100" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="100" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R1" s="100" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="S1" s="100" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T1" s="102" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -3597,14 +3590,14 @@
       </c>
       <c r="I2" s="96"/>
       <c r="K2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L2">
         <f t="array" ref="L2">SUMPRODUCT(--(LEN(TRIM(C2:C96))&gt;0))</f>
         <v>0</v>
       </c>
       <c r="N2" s="78" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O2" s="6">
         <f>COUNTIFS($B$2:$B$16,"摩登舞")</f>
@@ -3664,7 +3657,7 @@
       <c r="I3" s="96"/>
       <c r="K3" s="6"/>
       <c r="N3" s="104" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O3" s="104">
         <f>COUNTIFS($B$17:$B$31,"摩登舞")</f>
@@ -3723,14 +3716,14 @@
       </c>
       <c r="I4" s="96"/>
       <c r="K4" s="81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L4" s="82">
         <f>COUNTIF($D:$D,"慢")</f>
         <v>0</v>
       </c>
       <c r="N4" s="78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O4" s="78">
         <f>COUNTIFS($B$32:$B$51,"摩登舞")</f>
@@ -3789,7 +3782,7 @@
       </c>
       <c r="I5" s="96"/>
       <c r="K5" s="83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L5" s="84">
         <f>COUNTIF($D:$D,"中")</f>
@@ -3835,7 +3828,7 @@
       </c>
       <c r="I6" s="96"/>
       <c r="K6" s="79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L6" s="80">
         <f>COUNTIF($D:$D,"快")</f>
@@ -3914,14 +3907,14 @@
       </c>
       <c r="I8" s="96"/>
       <c r="K8" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L8" s="106">
         <f>COUNTIF($E:$E,"〿*")</f>
         <v>48</v>
       </c>
       <c r="N8" s="91" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O8" s="85">
         <f t="shared" ref="O8:T8" si="4">COUNTIFS($B$2:$B$52,O$1)</f>
@@ -3980,7 +3973,7 @@
       </c>
       <c r="I9" s="96"/>
       <c r="K9" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L9" s="106">
         <f>COUNTIF($H:$H,"⚠️*")</f>
@@ -4019,7 +4012,7 @@
       </c>
       <c r="I10" s="96"/>
       <c r="K10" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L10" s="106">
         <f>COUNTIF($G:$G,"⚠️*")</f>
@@ -4154,7 +4147,7 @@
       </c>
       <c r="I14" s="96"/>
       <c r="K14" s="107" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4189,7 +4182,7 @@
       </c>
       <c r="I15" s="96"/>
       <c r="K15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4224,7 +4217,7 @@
       </c>
       <c r="I16" s="96"/>
       <c r="K16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4259,7 +4252,7 @@
       </c>
       <c r="I17" s="96"/>
       <c r="K17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4294,7 +4287,7 @@
       </c>
       <c r="I18" s="96"/>
       <c r="K18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4329,7 +4322,7 @@
       </c>
       <c r="I19" s="96"/>
       <c r="K19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4364,7 +4357,7 @@
       </c>
       <c r="I20" s="96"/>
       <c r="K20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4399,7 +4392,7 @@
       </c>
       <c r="I21" s="96"/>
       <c r="K21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4434,7 +4427,7 @@
       </c>
       <c r="I22" s="96"/>
       <c r="K22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4469,7 +4462,7 @@
       </c>
       <c r="I23" s="96"/>
       <c r="K23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4504,7 +4497,7 @@
       </c>
       <c r="I24" s="96"/>
       <c r="K24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4539,7 +4532,7 @@
       </c>
       <c r="I25" s="96"/>
       <c r="K25" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4574,7 +4567,7 @@
       </c>
       <c r="I26" s="96"/>
       <c r="K26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4609,7 +4602,7 @@
       </c>
       <c r="I27" s="96"/>
       <c r="K27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4644,7 +4637,7 @@
       </c>
       <c r="I28" s="96"/>
       <c r="K28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4679,7 +4672,7 @@
       </c>
       <c r="I29" s="96"/>
       <c r="K29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4714,7 +4707,7 @@
       </c>
       <c r="I30" s="96"/>
       <c r="K30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4749,7 +4742,7 @@
       </c>
       <c r="I31" s="96"/>
       <c r="K31" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4784,7 +4777,7 @@
       </c>
       <c r="I32" s="96"/>
       <c r="K32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4819,7 +4812,7 @@
       </c>
       <c r="I33" s="96"/>
       <c r="K33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4854,7 +4847,7 @@
       </c>
       <c r="I34" s="96"/>
       <c r="K34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -4889,7 +4882,7 @@
       </c>
       <c r="I35" s="96"/>
       <c r="K35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
@@ -5543,34 +5536,34 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G1" s="73" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H1" s="73" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I1" s="77">
         <v>0.8125</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
@@ -7461,7 +7454,7 @@
         <v/>
       </c>
       <c r="C53" s="64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D53" s="64" t="str">
         <f>_xlfn.XLOOKUP($C53,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
@@ -7488,13 +7481,13 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.4">
       <c r="F54" s="71" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G54" s="72" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" s="72" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/舞曲排布_示例.xlsx
+++ b/舞曲排布_示例.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\jerome\git\Ballroom-Dance-Audio-Pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1541715-0389-4491-80FF-3041D0E00770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654B0B72-A888-4F8D-BC0F-677EDBA42E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="S0tsaS1mMDfAFeqK0JZS6UKbNMgI+lTtNJbr5tekb2B7WOpyvIjmJVxYhJDUOHU5ysUCb5N2a/+rTuwLul20dg==" workbookSaltValue="yrVN00eJ//IIPVqNHVJRQQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="舞种配比" sheetId="1" r:id="rId1"/>
@@ -1204,7 +1205,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1217,42 +1218,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1390,144 +1373,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1562,6 +1407,280 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="21" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2037,14 +2156,14 @@
   <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.1328125" style="6" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.3984375" style="6" customWidth="1"/>
-    <col min="8" max="8" width="16.33203125" style="116" customWidth="1"/>
-    <col min="9" max="9" width="65.1328125" style="116" customWidth="1"/>
+    <col min="1" max="1" width="8.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1328125" style="5" customWidth="1"/>
+    <col min="4" max="5" width="5.33203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.3984375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" style="64" customWidth="1"/>
+    <col min="9" max="9" width="65.1328125" style="64" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -2076,882 +2195,882 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:9" s="15" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="108">
+      <c r="D2" s="56">
         <v>3</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="16" t="s">
+      <c r="F2" s="12"/>
+      <c r="G2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:9" s="15" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="108">
+      <c r="D3" s="56">
         <v>2</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="22" t="s">
+      <c r="F3" s="12"/>
+      <c r="G3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:9" s="15" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="108">
+      <c r="D4" s="56">
         <v>1</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="22" t="s">
+      <c r="F4" s="12"/>
+      <c r="G4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:9" s="15" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="108">
+      <c r="D5" s="56">
         <v>1</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="16" t="s">
+      <c r="F5" s="12"/>
+      <c r="G5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="21" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:9" s="15" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="108">
+      <c r="D6" s="56">
         <v>1</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="22" t="s">
+      <c r="F6" s="12"/>
+      <c r="G6" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:9" s="24" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="109">
+      <c r="D7" s="57">
         <v>4</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="27" t="s">
+      <c r="F7" s="20"/>
+      <c r="G7" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:9" s="24" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="109">
+      <c r="D8" s="57">
         <v>3</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="24" t="s">
+      <c r="F8" s="20"/>
+      <c r="G8" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:9" s="24" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="109">
+      <c r="D9" s="57">
         <v>2</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="26"/>
-      <c r="G9" s="27" t="s">
+      <c r="F9" s="20"/>
+      <c r="G9" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+    <row r="10" spans="1:9" s="24" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="109">
+      <c r="D10" s="57">
         <v>1</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="26"/>
-      <c r="G10" s="27" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
+    <row r="11" spans="1:9" s="24" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="109">
+      <c r="D11" s="57">
         <v>1</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="26"/>
-      <c r="G11" s="27" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="28" t="s">
+      <c r="H11" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="I11" s="29" t="s">
+      <c r="I11" s="23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="36" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="31" t="s">
+    <row r="12" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="31" t="s">
+      <c r="C12" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12" s="58">
         <v>2</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="33" t="s">
+      <c r="F12" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="I12" s="35" t="s">
+      <c r="I12" s="29" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:9" s="36" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31" t="s">
+    <row r="13" spans="1:9" s="30" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="110">
+      <c r="D13" s="58">
         <v>2</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="33" t="s">
+      <c r="F13" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="34" t="s">
+      <c r="G13" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="35" t="s">
+      <c r="I13" s="29" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="37" t="s">
+    <row r="14" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="111">
+      <c r="D14" s="59">
         <v>3</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="I14" s="42" t="s">
+      <c r="I14" s="36" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="37" t="s">
+    <row r="15" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="37" t="s">
+      <c r="C15" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="111">
+      <c r="D15" s="59">
         <v>3</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="I15" s="42" t="s">
+      <c r="I15" s="36" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="37" t="s">
+    <row r="16" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="111">
+      <c r="D16" s="59">
         <v>1</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="39" t="s">
+      <c r="F16" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="42" t="s">
+      <c r="I16" s="36" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="37" t="s">
+    <row r="17" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="111">
+      <c r="D17" s="59">
         <v>1</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="39" t="s">
+      <c r="F17" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="40" t="s">
+      <c r="G17" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="I17" s="42" t="s">
+      <c r="I17" s="36" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="37" t="s">
+    <row r="18" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="111">
+      <c r="D18" s="59">
         <v>1</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="39" t="s">
+      <c r="F18" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="G18" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="42" t="s">
+      <c r="I18" s="36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="37" t="s">
+    <row r="19" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="111">
+      <c r="D19" s="59">
         <v>1</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="39" t="s">
+      <c r="F19" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="42" t="s">
+      <c r="I19" s="36" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="37" t="s">
+    <row r="20" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="111">
+      <c r="D20" s="59">
         <v>1</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="39" t="s">
+      <c r="F20" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="G20" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="H20" s="42" t="s">
+      <c r="H20" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="42" t="s">
+      <c r="I20" s="36" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="37" t="s">
+    <row r="21" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="111">
+      <c r="D21" s="59">
         <v>1</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="39" t="s">
+      <c r="F21" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="G21" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="I21" s="42" t="s">
+      <c r="I21" s="36" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="37" t="s">
+    <row r="22" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="44" t="s">
+      <c r="B22" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="111">
+      <c r="D22" s="59">
         <v>1</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="42" t="s">
+      <c r="F22" s="33"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="37" t="s">
+    <row r="23" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="44" t="s">
+      <c r="B23" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="111">
+      <c r="D23" s="59">
         <v>1</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="42" t="s">
+      <c r="F23" s="33"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="43" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="37" t="s">
+    <row r="24" spans="1:9" s="37" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="111">
+      <c r="D24" s="59">
         <v>1</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F24" s="39"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="42" t="s">
+      <c r="F24" s="33"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="36" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="46" t="s">
+    <row r="25" spans="1:9" s="46" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="112">
+      <c r="D25" s="60">
         <v>1</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="F25" s="48" t="s">
+      <c r="F25" s="42" t="s">
         <v>120</v>
       </c>
-      <c r="G25" s="49" t="s">
+      <c r="G25" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="H25" s="50" t="s">
+      <c r="H25" s="44" t="s">
         <v>122</v>
       </c>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="45" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="46" t="s">
+    <row r="26" spans="1:9" s="46" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="112">
+      <c r="D26" s="60">
         <v>1</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="46"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="51" t="s">
+      <c r="E26" s="41"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="45" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="46" t="s">
+    <row r="27" spans="1:9" s="46" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="112">
+      <c r="D27" s="60">
         <v>1</v>
       </c>
-      <c r="E27" s="47" t="s">
+      <c r="E27" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="H27" s="51" t="s">
+      <c r="H27" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="45" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="52" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="46" t="s">
+    <row r="28" spans="1:9" s="46" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="49" t="s">
+      <c r="B28" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="112">
+      <c r="D28" s="60">
         <v>1</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="50" t="s">
+      <c r="E28" s="41"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="45" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="60" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="54" t="s">
+    <row r="29" spans="1:9" s="54" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="54" t="s">
+      <c r="B29" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C29" s="54" t="s">
+      <c r="C29" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="113">
+      <c r="D29" s="61">
         <v>1</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="57" t="s">
+      <c r="F29" s="51" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="58" t="s">
+      <c r="G29" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="H29" s="59" t="s">
+      <c r="H29" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="I29" s="59" t="s">
+      <c r="I29" s="53" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="60" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="54" t="s">
+    <row r="30" spans="1:9" s="54" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="C30" s="54" t="s">
+      <c r="C30" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="113">
+      <c r="D30" s="61">
         <v>1</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="58"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="59" t="s">
+      <c r="F30" s="52"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="55"/>
+      <c r="I30" s="53" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="60" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="54" t="s">
+    <row r="31" spans="1:9" s="54" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="113">
+      <c r="D31" s="61">
         <v>1</v>
       </c>
-      <c r="E31" s="56" t="s">
+      <c r="E31" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="58"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="59"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="53"/>
     </row>
     <row r="32" spans="1:9" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="114">
-        <v>0</v>
-      </c>
-      <c r="E32" s="14"/>
-      <c r="F32" s="10" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="62">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G32" s="5"/>
+      <c r="G32" s="4"/>
       <c r="H32" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="I32" s="12"/>
+      <c r="I32" s="8"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D33" s="115"/>
+      <c r="D33" s="63"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D34" s="115"/>
+      <c r="D34" s="63"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D35" s="115"/>
+      <c r="D35" s="63"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D36" s="115"/>
+      <c r="D36" s="63"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D37" s="115"/>
+      <c r="D37" s="63"/>
     </row>
     <row r="38" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D38" s="115"/>
+      <c r="D38" s="63"/>
     </row>
     <row r="39" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D39" s="115"/>
+      <c r="D39" s="63"/>
     </row>
     <row r="40" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D40" s="115"/>
+      <c r="D40" s="63"/>
     </row>
     <row r="41" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D41" s="115"/>
+      <c r="D41" s="63"/>
     </row>
     <row r="42" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D42" s="115"/>
+      <c r="D42" s="63"/>
     </row>
     <row r="43" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D43" s="115"/>
+      <c r="D43" s="63"/>
     </row>
     <row r="44" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D44" s="115"/>
+      <c r="D44" s="63"/>
     </row>
     <row r="45" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D45" s="115"/>
+      <c r="D45" s="63"/>
     </row>
     <row r="46" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D46" s="115"/>
+      <c r="D46" s="63"/>
     </row>
     <row r="47" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D47" s="115"/>
+      <c r="D47" s="63"/>
     </row>
     <row r="48" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D48" s="115"/>
+      <c r="D48" s="63"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D49" s="115"/>
+      <c r="D49" s="63"/>
     </row>
     <row r="50" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D50" s="115"/>
+      <c r="D50" s="63"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2982,35 +3101,35 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="17.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" style="117" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.59765625" style="118" customWidth="1"/>
-    <col min="5" max="5" width="8.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="37.3984375" style="116" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.796875" style="116" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.19921875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.796875" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.59765625" style="66" customWidth="1"/>
+    <col min="5" max="5" width="8.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.3984375" style="64" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.796875" style="64" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="119" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="119" t="s">
+    <row r="1" spans="1:7" s="67" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="67" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="119" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="119" t="s">
+      <c r="D1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="119" t="s">
+      <c r="E1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="119" t="s">
+      <c r="F1" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="119" t="s">
+      <c r="G1" s="67" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3494,1975 +3613,1981 @@
   <dimension ref="A1:T55"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="12.59765625" style="116" customWidth="1"/>
-    <col min="5" max="9" width="10.59765625" style="116" customWidth="1"/>
-    <col min="11" max="11" width="10.53125" style="116" customWidth="1"/>
-    <col min="14" max="14" width="10.86328125" style="116" customWidth="1"/>
+    <col min="1" max="2" width="9.06640625" style="76"/>
+    <col min="3" max="3" width="12.59765625" style="101" customWidth="1"/>
+    <col min="4" max="4" width="9.06640625" style="76"/>
+    <col min="5" max="9" width="10.59765625" style="79" customWidth="1"/>
+    <col min="10" max="10" width="9.06640625" style="76"/>
+    <col min="11" max="11" width="10.53125" style="79" customWidth="1"/>
+    <col min="12" max="13" width="9.06640625" style="76"/>
+    <col min="14" max="14" width="10.86328125" style="79" customWidth="1"/>
+    <col min="15" max="16384" width="9.06640625" style="76"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="103" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:20" s="114" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="136" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="98" t="s">
+      <c r="B1" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="98" t="s">
+      <c r="C1" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="98" t="s">
+      <c r="D1" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="E1" s="110" t="s">
         <v>143</v>
       </c>
-      <c r="F1" s="99" t="s">
+      <c r="F1" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="99" t="s">
+      <c r="G1" s="110" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="99" t="s">
+      <c r="H1" s="110" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="99" t="s">
+      <c r="I1" s="110" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="100"/>
-      <c r="K1" s="101" t="s">
+      <c r="J1" s="111"/>
+      <c r="K1" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="L1" s="100" t="s">
+      <c r="L1" s="111" t="s">
         <v>148</v>
       </c>
-      <c r="M1" s="100"/>
-      <c r="N1" s="101" t="s">
+      <c r="M1" s="111"/>
+      <c r="N1" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="O1" s="100" t="s">
+      <c r="O1" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="P1" s="100" t="s">
+      <c r="P1" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="100" t="s">
+      <c r="Q1" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="R1" s="100" t="s">
+      <c r="R1" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="100" t="s">
+      <c r="S1" s="111" t="s">
         <v>118</v>
       </c>
-      <c r="T1" s="102" t="s">
+      <c r="T1" s="113" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="92">
+      <c r="A2" s="115">
         <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="92" t="str">
+      <c r="B2" s="115" t="str">
         <f>_xlfn.XLOOKUP($C2,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="92">
+      <c r="C2" s="106"/>
+      <c r="D2" s="115">
         <f>_xlfn.XLOOKUP($C2,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E2" s="105" t="str">
+      <c r="E2" s="116" t="str">
         <f t="shared" ref="E2:E33" si="1">IF(ROW()&lt;4, "OK", IF(AND(B3=B2, B2=B1), "〿相邻3次", "OK"))</f>
         <v>OK</v>
       </c>
-      <c r="F2" s="96" t="str">
+      <c r="F2" s="117" t="str">
         <f t="array" ref="F2">IF(COUNTIF(C$2:C2,C2)&gt;1, ROW()-MAX(IF(C$1:C1=C2,ROW(C$1:C1)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G2" s="96" t="str">
+      <c r="G2" s="117" t="str">
         <f t="shared" ref="G2:G33" si="2">IF(ROW()&gt;2, IF(D2=D1, "⚠️同节奏", "OK"), "OK")</f>
         <v>OK</v>
       </c>
-      <c r="H2" s="96" t="str">
+      <c r="H2" s="117" t="str">
         <f t="shared" ref="H2:H33" si="3">IF(F2="首次","",IF(F2&lt;5,"⚠️间隔"&amp;F2&amp;"首","间隔"&amp;F2&amp;"首✓"))</f>
         <v/>
       </c>
-      <c r="I2" s="96"/>
-      <c r="K2" s="6" t="s">
+      <c r="I2" s="117"/>
+      <c r="K2" s="80" t="s">
         <v>150</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="76">
         <f t="array" ref="L2">SUMPRODUCT(--(LEN(TRIM(C2:C96))&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="N2" s="78" t="s">
+      <c r="N2" s="118" t="s">
         <v>151</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="80">
         <f>COUNTIFS($B$2:$B$16,"摩登舞")</f>
         <v>0</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="80">
         <f>COUNTIFS($B$2:$B$16,"拉丁舞")</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="80">
         <f>COUNTIFS($B$2:$B$16,"地方舞")</f>
         <v>0</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="80">
         <f>COUNTIFS($B$2:$B$16,"交谊舞")</f>
         <v>0</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="80">
         <f>COUNTIFS($B$2:$B$16,"集体舞")</f>
         <v>0</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="80">
         <f>COUNTIFS($B$2:$B$16,"网红舞")</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="94">
+      <c r="A3" s="119">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B3" s="94" t="str">
+      <c r="B3" s="119" t="str">
         <f>_xlfn.XLOOKUP($C3,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="94">
+      <c r="C3" s="108"/>
+      <c r="D3" s="119">
         <f>_xlfn.XLOOKUP($C3,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E3" s="105" t="str">
+      <c r="E3" s="116" t="str">
         <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="F3" s="96" t="str">
+      <c r="F3" s="117" t="str">
         <f t="array" ref="F3">IF(COUNTIF(C$2:C3,C3)&gt;1, ROW()-MAX(IF(C$1:C2=C3,ROW(C$1:C2)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G3" s="96" t="str">
+      <c r="G3" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H3" s="96" t="str">
+      <c r="H3" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I3" s="96"/>
-      <c r="K3" s="6"/>
-      <c r="N3" s="104" t="s">
+      <c r="I3" s="117"/>
+      <c r="K3" s="80"/>
+      <c r="N3" s="120" t="s">
         <v>152</v>
       </c>
-      <c r="O3" s="104">
+      <c r="O3" s="120">
         <f>COUNTIFS($B$17:$B$31,"摩登舞")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="104">
+      <c r="P3" s="120">
         <f>COUNTIFS($B$17:$B$31,"拉丁舞")</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="104">
+      <c r="Q3" s="120">
         <f>COUNTIFS($B$17:$B$31,"地方舞")</f>
         <v>0</v>
       </c>
-      <c r="R3" s="104">
+      <c r="R3" s="120">
         <f>COUNTIFS($B$17:$B$31,"交谊舞")</f>
         <v>0</v>
       </c>
-      <c r="S3" s="104">
+      <c r="S3" s="120">
         <f>COUNTIFS($B$17:$B$31,"集体舞")</f>
         <v>0</v>
       </c>
-      <c r="T3" s="104">
+      <c r="T3" s="120">
         <f>COUNTIFS($B$17:$B$31,"网红舞")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="94">
+      <c r="A4" s="119">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="94" t="str">
+      <c r="B4" s="119" t="str">
         <f>_xlfn.XLOOKUP($C4,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C4" s="95"/>
-      <c r="D4" s="94">
+      <c r="C4" s="108"/>
+      <c r="D4" s="119">
         <f>_xlfn.XLOOKUP($C4,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="105" t="str">
+      <c r="E4" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F4" s="96" t="str">
+      <c r="F4" s="117" t="str">
         <f t="array" ref="F4">IF(COUNTIF(C$2:C4,C4)&gt;1, ROW()-MAX(IF(C$1:C3=C4,ROW(C$1:C3)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G4" s="96" t="str">
+      <c r="G4" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H4" s="96" t="str">
+      <c r="H4" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I4" s="96"/>
-      <c r="K4" s="81" t="s">
+      <c r="I4" s="117"/>
+      <c r="K4" s="121" t="s">
         <v>153</v>
       </c>
-      <c r="L4" s="82">
+      <c r="L4" s="122">
         <f>COUNTIF($D:$D,"慢")</f>
         <v>0</v>
       </c>
-      <c r="N4" s="78" t="s">
+      <c r="N4" s="118" t="s">
         <v>154</v>
       </c>
-      <c r="O4" s="78">
+      <c r="O4" s="118">
         <f>COUNTIFS($B$32:$B$51,"摩登舞")</f>
         <v>0</v>
       </c>
-      <c r="P4" s="78">
+      <c r="P4" s="118">
         <f>COUNTIFS($B$32:$B$51,"拉丁舞")</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="78">
+      <c r="Q4" s="118">
         <f>COUNTIFS($B$32:$B$51,"地方舞")</f>
         <v>0</v>
       </c>
-      <c r="R4" s="78">
+      <c r="R4" s="118">
         <f>COUNTIFS($B$32:$B$51,"交谊舞")</f>
         <v>0</v>
       </c>
-      <c r="S4" s="78">
+      <c r="S4" s="118">
         <f>COUNTIFS($B$32:$B$51,"集体舞")</f>
         <v>0</v>
       </c>
-      <c r="T4" s="78">
+      <c r="T4" s="118">
         <f>COUNTIFS($B$32:$B$51,"网红舞")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="94">
+      <c r="A5" s="119">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="94" t="str">
+      <c r="B5" s="119" t="str">
         <f>_xlfn.XLOOKUP($C5,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C5" s="95"/>
-      <c r="D5" s="94">
+      <c r="C5" s="108"/>
+      <c r="D5" s="119">
         <f>_xlfn.XLOOKUP($C5,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="105" t="str">
+      <c r="E5" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F5" s="96" t="str">
+      <c r="F5" s="117" t="str">
         <f t="array" ref="F5">IF(COUNTIF(C$2:C5,C5)&gt;1, ROW()-MAX(IF(C$1:C4=C5,ROW(C$1:C4)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G5" s="96" t="str">
+      <c r="G5" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H5" s="96" t="str">
+      <c r="H5" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I5" s="96"/>
-      <c r="K5" s="83" t="s">
+      <c r="I5" s="117"/>
+      <c r="K5" s="123" t="s">
         <v>155</v>
       </c>
-      <c r="L5" s="84">
+      <c r="L5" s="124">
         <f>COUNTIF($D:$D,"中")</f>
         <v>0</v>
       </c>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
-      <c r="R5" s="78"/>
-      <c r="S5" s="78"/>
-      <c r="T5" s="78"/>
+      <c r="N5" s="118"/>
+      <c r="O5" s="118"/>
+      <c r="P5" s="118"/>
+      <c r="Q5" s="118"/>
+      <c r="R5" s="118"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="118"/>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="94">
+      <c r="A6" s="119">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="94" t="str">
+      <c r="B6" s="119" t="str">
         <f>_xlfn.XLOOKUP($C6,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C6" s="95"/>
-      <c r="D6" s="94">
+      <c r="C6" s="108"/>
+      <c r="D6" s="119">
         <f>_xlfn.XLOOKUP($C6,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E6" s="105" t="str">
+      <c r="E6" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F6" s="96" t="str">
+      <c r="F6" s="117" t="str">
         <f t="array" ref="F6">IF(COUNTIF(C$2:C6,C6)&gt;1, ROW()-MAX(IF(C$1:C5=C6,ROW(C$1:C5)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G6" s="96" t="str">
+      <c r="G6" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H6" s="96" t="str">
+      <c r="H6" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I6" s="96"/>
-      <c r="K6" s="79" t="s">
+      <c r="I6" s="117"/>
+      <c r="K6" s="125" t="s">
         <v>156</v>
       </c>
-      <c r="L6" s="80">
+      <c r="L6" s="126">
         <f>COUNTIF($D:$D,"快")</f>
         <v>0</v>
       </c>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
-      <c r="R6" s="78"/>
-      <c r="S6" s="78"/>
-      <c r="T6" s="78"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="118"/>
+      <c r="R6" s="118"/>
+      <c r="S6" s="118"/>
+      <c r="T6" s="118"/>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="94">
+      <c r="A7" s="119">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="94" t="str">
+      <c r="B7" s="119" t="str">
         <f>_xlfn.XLOOKUP($C7,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="94">
+      <c r="C7" s="108"/>
+      <c r="D7" s="119">
         <f>_xlfn.XLOOKUP($C7,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E7" s="105" t="str">
+      <c r="E7" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F7" s="96" t="str">
+      <c r="F7" s="117" t="str">
         <f t="array" ref="F7">IF(COUNTIF(C$2:C7,C7)&gt;1, ROW()-MAX(IF(C$1:C6=C7,ROW(C$1:C6)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G7" s="96" t="str">
+      <c r="G7" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H7" s="96" t="str">
+      <c r="H7" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I7" s="96"/>
-      <c r="K7" s="6"/>
+      <c r="I7" s="117"/>
+      <c r="K7" s="80"/>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="94">
+      <c r="A8" s="119">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="94" t="str">
+      <c r="B8" s="119" t="str">
         <f>_xlfn.XLOOKUP($C8,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C8" s="95"/>
-      <c r="D8" s="94">
+      <c r="C8" s="108"/>
+      <c r="D8" s="119">
         <f>_xlfn.XLOOKUP($C8,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E8" s="105" t="str">
+      <c r="E8" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F8" s="96" t="str">
+      <c r="F8" s="117" t="str">
         <f t="array" ref="F8">IF(COUNTIF(C$2:C8,C8)&gt;1, ROW()-MAX(IF(C$1:C7=C8,ROW(C$1:C7)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G8" s="96" t="str">
+      <c r="G8" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H8" s="96" t="str">
+      <c r="H8" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I8" s="96"/>
-      <c r="K8" s="6" t="s">
+      <c r="I8" s="117"/>
+      <c r="K8" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="L8" s="106">
+      <c r="L8" s="127">
         <f>COUNTIF($E:$E,"〿*")</f>
         <v>48</v>
       </c>
-      <c r="N8" s="91" t="s">
+      <c r="N8" s="128" t="s">
         <v>158</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="129">
         <f t="shared" ref="O8:T8" si="4">COUNTIFS($B$2:$B$52,O$1)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="130">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="131">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="132">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S8" s="88">
+      <c r="S8" s="133">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T8" s="89">
+      <c r="T8" s="134">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="94">
+      <c r="A9" s="119">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="94" t="str">
+      <c r="B9" s="119" t="str">
         <f>_xlfn.XLOOKUP($C9,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C9" s="95"/>
-      <c r="D9" s="94">
+      <c r="C9" s="108"/>
+      <c r="D9" s="119">
         <f>_xlfn.XLOOKUP($C9,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E9" s="105" t="str">
+      <c r="E9" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F9" s="96" t="str">
+      <c r="F9" s="117" t="str">
         <f t="array" ref="F9">IF(COUNTIF(C$2:C9,C9)&gt;1, ROW()-MAX(IF(C$1:C8=C9,ROW(C$1:C8)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G9" s="96" t="str">
+      <c r="G9" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H9" s="96" t="str">
+      <c r="H9" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I9" s="96"/>
-      <c r="K9" s="6" t="s">
+      <c r="I9" s="117"/>
+      <c r="K9" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="L9" s="106">
+      <c r="L9" s="127">
         <f>COUNTIF($H:$H,"⚠️*")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="94">
+      <c r="A10" s="119">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="94" t="str">
+      <c r="B10" s="119" t="str">
         <f>_xlfn.XLOOKUP($C10,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="94">
+      <c r="C10" s="108"/>
+      <c r="D10" s="119">
         <f>_xlfn.XLOOKUP($C10,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E10" s="105" t="str">
+      <c r="E10" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F10" s="96" t="str">
+      <c r="F10" s="117" t="str">
         <f t="array" ref="F10">IF(COUNTIF(C$2:C10,C10)&gt;1, ROW()-MAX(IF(C$1:C9=C10,ROW(C$1:C9)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G10" s="96" t="str">
+      <c r="G10" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H10" s="96" t="str">
+      <c r="H10" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I10" s="96"/>
-      <c r="K10" s="6" t="s">
+      <c r="I10" s="117"/>
+      <c r="K10" s="80" t="s">
         <v>160</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="127">
         <f>COUNTIF($G:$G,"⚠️*")</f>
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="94">
+      <c r="A11" s="119">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="94" t="str">
+      <c r="B11" s="119" t="str">
         <f>_xlfn.XLOOKUP($C11,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C11" s="95"/>
-      <c r="D11" s="94">
+      <c r="C11" s="108"/>
+      <c r="D11" s="119">
         <f>_xlfn.XLOOKUP($C11,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E11" s="105" t="str">
+      <c r="E11" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F11" s="96" t="str">
+      <c r="F11" s="117" t="str">
         <f t="array" ref="F11">IF(COUNTIF(C$2:C11,C11)&gt;1, ROW()-MAX(IF(C$1:C10=C11,ROW(C$1:C10)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G11" s="96" t="str">
+      <c r="G11" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H11" s="96" t="str">
+      <c r="H11" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I11" s="96"/>
+      <c r="I11" s="117"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="94">
+      <c r="A12" s="119">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="94" t="str">
+      <c r="B12" s="119" t="str">
         <f>_xlfn.XLOOKUP($C12,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C12" s="95"/>
-      <c r="D12" s="94">
+      <c r="C12" s="108"/>
+      <c r="D12" s="119">
         <f>_xlfn.XLOOKUP($C12,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E12" s="105" t="str">
+      <c r="E12" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F12" s="96" t="str">
+      <c r="F12" s="117" t="str">
         <f t="array" ref="F12">IF(COUNTIF(C$2:C12,C12)&gt;1, ROW()-MAX(IF(C$1:C11=C12,ROW(C$1:C11)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G12" s="96" t="str">
+      <c r="G12" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H12" s="96" t="str">
+      <c r="H12" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I12" s="96"/>
+      <c r="I12" s="117"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="94">
+      <c r="A13" s="119">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="94" t="str">
+      <c r="B13" s="119" t="str">
         <f>_xlfn.XLOOKUP($C13,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C13" s="95"/>
-      <c r="D13" s="94">
+      <c r="C13" s="108"/>
+      <c r="D13" s="119">
         <f>_xlfn.XLOOKUP($C13,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E13" s="105" t="str">
+      <c r="E13" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F13" s="96" t="str">
+      <c r="F13" s="117" t="str">
         <f t="array" ref="F13">IF(COUNTIF(C$2:C13,C13)&gt;1, ROW()-MAX(IF(C$1:C12=C13,ROW(C$1:C12)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G13" s="96" t="str">
+      <c r="G13" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H13" s="96" t="str">
+      <c r="H13" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I13" s="96"/>
+      <c r="I13" s="117"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="94">
+      <c r="A14" s="119">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="94" t="str">
+      <c r="B14" s="119" t="str">
         <f>_xlfn.XLOOKUP($C14,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="94">
+      <c r="C14" s="108"/>
+      <c r="D14" s="119">
         <f>_xlfn.XLOOKUP($C14,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E14" s="105" t="str">
+      <c r="E14" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F14" s="96" t="str">
+      <c r="F14" s="117" t="str">
         <f t="array" ref="F14">IF(COUNTIF(C$2:C14,C14)&gt;1, ROW()-MAX(IF(C$1:C13=C14,ROW(C$1:C13)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G14" s="96" t="str">
+      <c r="G14" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H14" s="96" t="str">
+      <c r="H14" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I14" s="96"/>
-      <c r="K14" s="107" t="s">
+      <c r="I14" s="117"/>
+      <c r="K14" s="135" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="94">
+      <c r="A15" s="119">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="94" t="str">
+      <c r="B15" s="119" t="str">
         <f>_xlfn.XLOOKUP($C15,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="94">
+      <c r="C15" s="108"/>
+      <c r="D15" s="119">
         <f>_xlfn.XLOOKUP($C15,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="105" t="str">
+      <c r="E15" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F15" s="96" t="str">
+      <c r="F15" s="117" t="str">
         <f t="array" ref="F15">IF(COUNTIF(C$2:C15,C15)&gt;1, ROW()-MAX(IF(C$1:C14=C15,ROW(C$1:C14)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G15" s="96" t="str">
+      <c r="G15" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H15" s="96" t="str">
+      <c r="H15" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I15" s="96"/>
-      <c r="K15" t="s">
+      <c r="I15" s="117"/>
+      <c r="K15" s="76" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="94">
+      <c r="A16" s="119">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="94" t="str">
+      <c r="B16" s="119" t="str">
         <f>_xlfn.XLOOKUP($C16,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C16" s="95"/>
-      <c r="D16" s="94">
+      <c r="C16" s="108"/>
+      <c r="D16" s="119">
         <f>_xlfn.XLOOKUP($C16,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="105" t="str">
+      <c r="E16" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F16" s="96" t="str">
+      <c r="F16" s="117" t="str">
         <f t="array" ref="F16">IF(COUNTIF(C$2:C16,C16)&gt;1, ROW()-MAX(IF(C$1:C15=C16,ROW(C$1:C15)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G16" s="96" t="str">
+      <c r="G16" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H16" s="96" t="str">
+      <c r="H16" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I16" s="96"/>
-      <c r="K16" t="s">
+      <c r="I16" s="117"/>
+      <c r="K16" s="76" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="94">
+      <c r="A17" s="119">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="94" t="str">
+      <c r="B17" s="119" t="str">
         <f>_xlfn.XLOOKUP($C17,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C17" s="95"/>
-      <c r="D17" s="94">
+      <c r="C17" s="108"/>
+      <c r="D17" s="119">
         <f>_xlfn.XLOOKUP($C17,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E17" s="105" t="str">
+      <c r="E17" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F17" s="96" t="str">
+      <c r="F17" s="117" t="str">
         <f t="array" ref="F17">IF(COUNTIF(C$2:C17,C17)&gt;1, ROW()-MAX(IF(C$1:C16=C17,ROW(C$1:C16)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G17" s="96" t="str">
+      <c r="G17" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H17" s="96" t="str">
+      <c r="H17" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I17" s="96"/>
-      <c r="K17" t="s">
+      <c r="I17" s="117"/>
+      <c r="K17" s="76" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="94">
+      <c r="A18" s="119">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="94" t="str">
+      <c r="B18" s="119" t="str">
         <f>_xlfn.XLOOKUP($C18,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C18" s="95"/>
-      <c r="D18" s="94">
+      <c r="C18" s="108"/>
+      <c r="D18" s="119">
         <f>_xlfn.XLOOKUP($C18,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="105" t="str">
+      <c r="E18" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F18" s="96" t="str">
+      <c r="F18" s="117" t="str">
         <f t="array" ref="F18">IF(COUNTIF(C$2:C18,C18)&gt;1, ROW()-MAX(IF(C$1:C17=C18,ROW(C$1:C17)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G18" s="96" t="str">
+      <c r="G18" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H18" s="96" t="str">
+      <c r="H18" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I18" s="96"/>
-      <c r="K18" t="s">
+      <c r="I18" s="117"/>
+      <c r="K18" s="76" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="94">
+      <c r="A19" s="119">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="94" t="str">
+      <c r="B19" s="119" t="str">
         <f>_xlfn.XLOOKUP($C19,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C19" s="95"/>
-      <c r="D19" s="94">
+      <c r="C19" s="108"/>
+      <c r="D19" s="119">
         <f>_xlfn.XLOOKUP($C19,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="105" t="str">
+      <c r="E19" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F19" s="96" t="str">
+      <c r="F19" s="117" t="str">
         <f t="array" ref="F19">IF(COUNTIF(C$2:C19,C19)&gt;1, ROW()-MAX(IF(C$1:C18=C19,ROW(C$1:C18)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G19" s="96" t="str">
+      <c r="G19" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H19" s="96" t="str">
+      <c r="H19" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I19" s="96"/>
-      <c r="K19" t="s">
+      <c r="I19" s="117"/>
+      <c r="K19" s="76" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="94">
+      <c r="A20" s="119">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="94" t="str">
+      <c r="B20" s="119" t="str">
         <f>_xlfn.XLOOKUP($C20,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C20" s="95"/>
-      <c r="D20" s="94">
+      <c r="C20" s="108"/>
+      <c r="D20" s="119">
         <f>_xlfn.XLOOKUP($C20,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="105" t="str">
+      <c r="E20" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F20" s="96" t="str">
+      <c r="F20" s="117" t="str">
         <f t="array" ref="F20">IF(COUNTIF(C$2:C20,C20)&gt;1, ROW()-MAX(IF(C$1:C19=C20,ROW(C$1:C19)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G20" s="96" t="str">
+      <c r="G20" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H20" s="96" t="str">
+      <c r="H20" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I20" s="96"/>
-      <c r="K20" t="s">
+      <c r="I20" s="117"/>
+      <c r="K20" s="76" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="94">
+      <c r="A21" s="119">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="94" t="str">
+      <c r="B21" s="119" t="str">
         <f>_xlfn.XLOOKUP($C21,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C21" s="95"/>
-      <c r="D21" s="94">
+      <c r="C21" s="108"/>
+      <c r="D21" s="119">
         <f>_xlfn.XLOOKUP($C21,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="105" t="str">
+      <c r="E21" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F21" s="96" t="str">
+      <c r="F21" s="117" t="str">
         <f t="array" ref="F21">IF(COUNTIF(C$2:C21,C21)&gt;1, ROW()-MAX(IF(C$1:C20=C21,ROW(C$1:C20)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G21" s="96" t="str">
+      <c r="G21" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H21" s="96" t="str">
+      <c r="H21" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I21" s="96"/>
-      <c r="K21" t="s">
+      <c r="I21" s="117"/>
+      <c r="K21" s="76" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="94">
+      <c r="A22" s="119">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="94" t="str">
+      <c r="B22" s="119" t="str">
         <f>_xlfn.XLOOKUP($C22,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C22" s="95"/>
-      <c r="D22" s="94">
+      <c r="C22" s="108"/>
+      <c r="D22" s="119">
         <f>_xlfn.XLOOKUP($C22,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E22" s="105" t="str">
+      <c r="E22" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F22" s="96" t="str">
+      <c r="F22" s="117" t="str">
         <f t="array" ref="F22">IF(COUNTIF(C$2:C22,C22)&gt;1, ROW()-MAX(IF(C$1:C21=C22,ROW(C$1:C21)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G22" s="96" t="str">
+      <c r="G22" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H22" s="96" t="str">
+      <c r="H22" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I22" s="96"/>
-      <c r="K22" t="s">
+      <c r="I22" s="117"/>
+      <c r="K22" s="76" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="94">
+      <c r="A23" s="119">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="94" t="str">
+      <c r="B23" s="119" t="str">
         <f>_xlfn.XLOOKUP($C23,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C23" s="95"/>
-      <c r="D23" s="94">
+      <c r="C23" s="108"/>
+      <c r="D23" s="119">
         <f>_xlfn.XLOOKUP($C23,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E23" s="105" t="str">
+      <c r="E23" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F23" s="96" t="str">
+      <c r="F23" s="117" t="str">
         <f t="array" ref="F23">IF(COUNTIF(C$2:C23,C23)&gt;1, ROW()-MAX(IF(C$1:C22=C23,ROW(C$1:C22)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G23" s="96" t="str">
+      <c r="G23" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H23" s="96" t="str">
+      <c r="H23" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I23" s="96"/>
-      <c r="K23" t="s">
+      <c r="I23" s="117"/>
+      <c r="K23" s="76" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="94">
+      <c r="A24" s="119">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="94" t="str">
+      <c r="B24" s="119" t="str">
         <f>_xlfn.XLOOKUP($C24,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C24" s="95"/>
-      <c r="D24" s="94">
+      <c r="C24" s="108"/>
+      <c r="D24" s="119">
         <f>_xlfn.XLOOKUP($C24,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E24" s="105" t="str">
+      <c r="E24" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F24" s="96" t="str">
+      <c r="F24" s="117" t="str">
         <f t="array" ref="F24">IF(COUNTIF(C$2:C24,C24)&gt;1, ROW()-MAX(IF(C$1:C23=C24,ROW(C$1:C23)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G24" s="96" t="str">
+      <c r="G24" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H24" s="96" t="str">
+      <c r="H24" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I24" s="96"/>
-      <c r="K24" t="s">
+      <c r="I24" s="117"/>
+      <c r="K24" s="76" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="94">
+      <c r="A25" s="119">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="94" t="str">
+      <c r="B25" s="119" t="str">
         <f>_xlfn.XLOOKUP($C25,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C25" s="95"/>
-      <c r="D25" s="94">
+      <c r="C25" s="108"/>
+      <c r="D25" s="119">
         <f>_xlfn.XLOOKUP($C25,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="105" t="str">
+      <c r="E25" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F25" s="96" t="str">
+      <c r="F25" s="117" t="str">
         <f t="array" ref="F25">IF(COUNTIF(C$2:C25,C25)&gt;1, ROW()-MAX(IF(C$1:C24=C25,ROW(C$1:C24)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G25" s="96" t="str">
+      <c r="G25" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H25" s="96" t="str">
+      <c r="H25" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I25" s="96"/>
-      <c r="K25" t="s">
+      <c r="I25" s="117"/>
+      <c r="K25" s="76" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="94">
+      <c r="A26" s="119">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="94" t="str">
+      <c r="B26" s="119" t="str">
         <f>_xlfn.XLOOKUP($C26,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C26" s="95"/>
-      <c r="D26" s="94">
+      <c r="C26" s="108"/>
+      <c r="D26" s="119">
         <f>_xlfn.XLOOKUP($C26,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E26" s="105" t="str">
+      <c r="E26" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F26" s="96" t="str">
+      <c r="F26" s="117" t="str">
         <f t="array" ref="F26">IF(COUNTIF(C$2:C26,C26)&gt;1, ROW()-MAX(IF(C$1:C25=C26,ROW(C$1:C25)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G26" s="96" t="str">
+      <c r="G26" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H26" s="96" t="str">
+      <c r="H26" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I26" s="96"/>
-      <c r="K26" t="s">
+      <c r="I26" s="117"/>
+      <c r="K26" s="76" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="94">
+      <c r="A27" s="119">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="94" t="str">
+      <c r="B27" s="119" t="str">
         <f>_xlfn.XLOOKUP($C27,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C27" s="95"/>
-      <c r="D27" s="94">
+      <c r="C27" s="108"/>
+      <c r="D27" s="119">
         <f>_xlfn.XLOOKUP($C27,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E27" s="105" t="str">
+      <c r="E27" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F27" s="96" t="str">
+      <c r="F27" s="117" t="str">
         <f t="array" ref="F27">IF(COUNTIF(C$2:C27,C27)&gt;1, ROW()-MAX(IF(C$1:C26=C27,ROW(C$1:C26)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G27" s="96" t="str">
+      <c r="G27" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H27" s="96" t="str">
+      <c r="H27" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I27" s="96"/>
-      <c r="K27" t="s">
+      <c r="I27" s="117"/>
+      <c r="K27" s="76" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="94">
+      <c r="A28" s="119">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="94" t="str">
+      <c r="B28" s="119" t="str">
         <f>_xlfn.XLOOKUP($C28,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C28" s="95"/>
-      <c r="D28" s="94">
+      <c r="C28" s="108"/>
+      <c r="D28" s="119">
         <f>_xlfn.XLOOKUP($C28,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E28" s="105" t="str">
+      <c r="E28" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F28" s="96" t="str">
+      <c r="F28" s="117" t="str">
         <f t="array" ref="F28">IF(COUNTIF(C$2:C28,C28)&gt;1, ROW()-MAX(IF(C$1:C27=C28,ROW(C$1:C27)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G28" s="96" t="str">
+      <c r="G28" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H28" s="96" t="str">
+      <c r="H28" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I28" s="96"/>
-      <c r="K28" t="s">
+      <c r="I28" s="117"/>
+      <c r="K28" s="76" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="94">
+      <c r="A29" s="119">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="94" t="str">
+      <c r="B29" s="119" t="str">
         <f>_xlfn.XLOOKUP($C29,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C29" s="95"/>
-      <c r="D29" s="94">
+      <c r="C29" s="108"/>
+      <c r="D29" s="119">
         <f>_xlfn.XLOOKUP($C29,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E29" s="105" t="str">
+      <c r="E29" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F29" s="96" t="str">
+      <c r="F29" s="117" t="str">
         <f t="array" ref="F29">IF(COUNTIF(C$2:C29,C29)&gt;1, ROW()-MAX(IF(C$1:C28=C29,ROW(C$1:C28)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G29" s="96" t="str">
+      <c r="G29" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H29" s="96" t="str">
+      <c r="H29" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I29" s="96"/>
-      <c r="K29" t="s">
+      <c r="I29" s="117"/>
+      <c r="K29" s="76" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="94">
+      <c r="A30" s="119">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="94" t="str">
+      <c r="B30" s="119" t="str">
         <f>_xlfn.XLOOKUP($C30,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C30" s="95"/>
-      <c r="D30" s="94">
+      <c r="C30" s="108"/>
+      <c r="D30" s="119">
         <f>_xlfn.XLOOKUP($C30,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="105" t="str">
+      <c r="E30" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F30" s="96" t="str">
+      <c r="F30" s="117" t="str">
         <f t="array" ref="F30">IF(COUNTIF(C$2:C30,C30)&gt;1, ROW()-MAX(IF(C$1:C29=C30,ROW(C$1:C29)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G30" s="96" t="str">
+      <c r="G30" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H30" s="96" t="str">
+      <c r="H30" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I30" s="96"/>
-      <c r="K30" t="s">
+      <c r="I30" s="117"/>
+      <c r="K30" s="76" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="94">
+      <c r="A31" s="119">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="94" t="str">
+      <c r="B31" s="119" t="str">
         <f>_xlfn.XLOOKUP($C31,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C31" s="95"/>
-      <c r="D31" s="94">
+      <c r="C31" s="108"/>
+      <c r="D31" s="119">
         <f>_xlfn.XLOOKUP($C31,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E31" s="105" t="str">
+      <c r="E31" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F31" s="96" t="str">
+      <c r="F31" s="117" t="str">
         <f t="array" ref="F31">IF(COUNTIF(C$2:C31,C31)&gt;1, ROW()-MAX(IF(C$1:C30=C31,ROW(C$1:C30)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G31" s="96" t="str">
+      <c r="G31" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H31" s="96" t="str">
+      <c r="H31" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I31" s="96"/>
-      <c r="K31" t="s">
+      <c r="I31" s="117"/>
+      <c r="K31" s="76" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="94">
+      <c r="A32" s="119">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="94" t="str">
+      <c r="B32" s="119" t="str">
         <f>_xlfn.XLOOKUP($C32,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C32" s="95"/>
-      <c r="D32" s="94">
+      <c r="C32" s="108"/>
+      <c r="D32" s="119">
         <f>_xlfn.XLOOKUP($C32,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E32" s="105" t="str">
+      <c r="E32" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F32" s="96" t="str">
+      <c r="F32" s="117" t="str">
         <f t="array" ref="F32">IF(COUNTIF(C$2:C32,C32)&gt;1, ROW()-MAX(IF(C$1:C31=C32,ROW(C$1:C31)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G32" s="96" t="str">
+      <c r="G32" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H32" s="96" t="str">
+      <c r="H32" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I32" s="96"/>
-      <c r="K32" t="s">
+      <c r="I32" s="117"/>
+      <c r="K32" s="76" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="94">
+      <c r="A33" s="119">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="94" t="str">
+      <c r="B33" s="119" t="str">
         <f>_xlfn.XLOOKUP($C33,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C33" s="95"/>
-      <c r="D33" s="94">
+      <c r="C33" s="108"/>
+      <c r="D33" s="119">
         <f>_xlfn.XLOOKUP($C33,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E33" s="105" t="str">
+      <c r="E33" s="116" t="str">
         <f t="shared" si="1"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F33" s="96" t="str">
+      <c r="F33" s="117" t="str">
         <f t="array" ref="F33">IF(COUNTIF(C$2:C33,C33)&gt;1, ROW()-MAX(IF(C$1:C32=C33,ROW(C$1:C32)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G33" s="96" t="str">
+      <c r="G33" s="117" t="str">
         <f t="shared" si="2"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H33" s="96" t="str">
+      <c r="H33" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I33" s="96"/>
-      <c r="K33" t="s">
+      <c r="I33" s="117"/>
+      <c r="K33" s="76" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="94">
+      <c r="A34" s="119">
         <f t="shared" ref="A34:A52" si="5">ROW()-1</f>
         <v>33</v>
       </c>
-      <c r="B34" s="94" t="str">
+      <c r="B34" s="119" t="str">
         <f>_xlfn.XLOOKUP($C34,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C34" s="95"/>
-      <c r="D34" s="94">
+      <c r="C34" s="108"/>
+      <c r="D34" s="119">
         <f>_xlfn.XLOOKUP($C34,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E34" s="105" t="str">
+      <c r="E34" s="116" t="str">
         <f t="shared" ref="E34:E52" si="6">IF(ROW()&lt;4, "OK", IF(AND(B35=B34, B34=B33), "〿相邻3次", "OK"))</f>
         <v>〿相邻3次</v>
       </c>
-      <c r="F34" s="96" t="str">
+      <c r="F34" s="117" t="str">
         <f t="array" ref="F34">IF(COUNTIF(C$2:C34,C34)&gt;1, ROW()-MAX(IF(C$1:C33=C34,ROW(C$1:C33)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G34" s="96" t="str">
+      <c r="G34" s="117" t="str">
         <f t="shared" ref="G34:G52" si="7">IF(ROW()&gt;2, IF(D34=D33, "⚠️同节奏", "OK"), "OK")</f>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H34" s="96" t="str">
+      <c r="H34" s="117" t="str">
         <f t="shared" ref="H34:H52" si="8">IF(F34="首次","",IF(F34&lt;5,"⚠️间隔"&amp;F34&amp;"首","间隔"&amp;F34&amp;"首✓"))</f>
         <v/>
       </c>
-      <c r="I34" s="96"/>
-      <c r="K34" t="s">
+      <c r="I34" s="117"/>
+      <c r="K34" s="76" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="94">
+      <c r="A35" s="119">
         <f t="shared" si="5"/>
         <v>34</v>
       </c>
-      <c r="B35" s="94" t="str">
+      <c r="B35" s="119" t="str">
         <f>_xlfn.XLOOKUP($C35,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C35" s="95"/>
-      <c r="D35" s="94">
+      <c r="C35" s="108"/>
+      <c r="D35" s="119">
         <f>_xlfn.XLOOKUP($C35,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E35" s="105" t="str">
+      <c r="E35" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F35" s="96" t="str">
+      <c r="F35" s="117" t="str">
         <f t="array" ref="F35">IF(COUNTIF(C$2:C35,C35)&gt;1, ROW()-MAX(IF(C$1:C34=C35,ROW(C$1:C34)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G35" s="96" t="str">
+      <c r="G35" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H35" s="96" t="str">
+      <c r="H35" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I35" s="96"/>
-      <c r="K35" t="s">
+      <c r="I35" s="117"/>
+      <c r="K35" s="76" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="94">
+      <c r="A36" s="119">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="B36" s="94" t="str">
+      <c r="B36" s="119" t="str">
         <f>_xlfn.XLOOKUP($C36,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C36" s="95"/>
-      <c r="D36" s="94">
+      <c r="C36" s="108"/>
+      <c r="D36" s="119">
         <f>_xlfn.XLOOKUP($C36,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E36" s="105" t="str">
+      <c r="E36" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F36" s="96" t="str">
+      <c r="F36" s="117" t="str">
         <f t="array" ref="F36">IF(COUNTIF(C$2:C36,C36)&gt;1, ROW()-MAX(IF(C$1:C35=C36,ROW(C$1:C35)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G36" s="96" t="str">
+      <c r="G36" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H36" s="96" t="str">
+      <c r="H36" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I36" s="96"/>
+      <c r="I36" s="117"/>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="94">
+      <c r="A37" s="119">
         <f t="shared" si="5"/>
         <v>36</v>
       </c>
-      <c r="B37" s="94" t="str">
+      <c r="B37" s="119" t="str">
         <f>_xlfn.XLOOKUP($C37,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C37" s="95"/>
-      <c r="D37" s="94">
+      <c r="C37" s="108"/>
+      <c r="D37" s="119">
         <f>_xlfn.XLOOKUP($C37,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="105" t="str">
+      <c r="E37" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F37" s="96" t="str">
+      <c r="F37" s="117" t="str">
         <f t="array" ref="F37">IF(COUNTIF(C$2:C37,C37)&gt;1, ROW()-MAX(IF(C$1:C36=C37,ROW(C$1:C36)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G37" s="96" t="str">
+      <c r="G37" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H37" s="96" t="str">
+      <c r="H37" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I37" s="96"/>
+      <c r="I37" s="117"/>
     </row>
     <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="94">
+      <c r="A38" s="119">
         <f t="shared" si="5"/>
         <v>37</v>
       </c>
-      <c r="B38" s="94" t="str">
+      <c r="B38" s="119" t="str">
         <f>_xlfn.XLOOKUP($C38,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C38" s="95"/>
-      <c r="D38" s="94">
+      <c r="C38" s="108"/>
+      <c r="D38" s="119">
         <f>_xlfn.XLOOKUP($C38,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E38" s="105" t="str">
+      <c r="E38" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F38" s="96" t="str">
+      <c r="F38" s="117" t="str">
         <f t="array" ref="F38">IF(COUNTIF(C$2:C38,C38)&gt;1, ROW()-MAX(IF(C$1:C37=C38,ROW(C$1:C37)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G38" s="96" t="str">
+      <c r="G38" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H38" s="96" t="str">
+      <c r="H38" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I38" s="96"/>
+      <c r="I38" s="117"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="94">
+      <c r="A39" s="119">
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="B39" s="94" t="str">
+      <c r="B39" s="119" t="str">
         <f>_xlfn.XLOOKUP($C39,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C39" s="95"/>
-      <c r="D39" s="94">
+      <c r="C39" s="108"/>
+      <c r="D39" s="119">
         <f>_xlfn.XLOOKUP($C39,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E39" s="105" t="str">
+      <c r="E39" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F39" s="96" t="str">
+      <c r="F39" s="117" t="str">
         <f t="array" ref="F39">IF(COUNTIF(C$2:C39,C39)&gt;1, ROW()-MAX(IF(C$1:C38=C39,ROW(C$1:C38)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G39" s="96" t="str">
+      <c r="G39" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H39" s="96" t="str">
+      <c r="H39" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I39" s="96"/>
+      <c r="I39" s="117"/>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="94">
+      <c r="A40" s="119">
         <f t="shared" si="5"/>
         <v>39</v>
       </c>
-      <c r="B40" s="94" t="str">
+      <c r="B40" s="119" t="str">
         <f>_xlfn.XLOOKUP($C40,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C40" s="95"/>
-      <c r="D40" s="94">
+      <c r="C40" s="108"/>
+      <c r="D40" s="119">
         <f>_xlfn.XLOOKUP($C40,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E40" s="105" t="str">
+      <c r="E40" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F40" s="96" t="str">
+      <c r="F40" s="117" t="str">
         <f t="array" ref="F40">IF(COUNTIF(C$2:C40,C40)&gt;1, ROW()-MAX(IF(C$1:C39=C40,ROW(C$1:C39)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G40" s="96" t="str">
+      <c r="G40" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H40" s="96" t="str">
+      <c r="H40" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I40" s="96"/>
+      <c r="I40" s="117"/>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="94">
+      <c r="A41" s="119">
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="B41" s="94" t="str">
+      <c r="B41" s="119" t="str">
         <f>_xlfn.XLOOKUP($C41,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C41" s="95"/>
-      <c r="D41" s="94">
+      <c r="C41" s="108"/>
+      <c r="D41" s="119">
         <f>_xlfn.XLOOKUP($C41,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E41" s="105" t="str">
+      <c r="E41" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F41" s="96" t="str">
+      <c r="F41" s="117" t="str">
         <f t="array" ref="F41">IF(COUNTIF(C$2:C41,C41)&gt;1, ROW()-MAX(IF(C$1:C40=C41,ROW(C$1:C40)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G41" s="96" t="str">
+      <c r="G41" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H41" s="96" t="str">
+      <c r="H41" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I41" s="96"/>
+      <c r="I41" s="117"/>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="94">
+      <c r="A42" s="119">
         <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="B42" s="94" t="str">
+      <c r="B42" s="119" t="str">
         <f>_xlfn.XLOOKUP($C42,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C42" s="95"/>
-      <c r="D42" s="94">
+      <c r="C42" s="108"/>
+      <c r="D42" s="119">
         <f>_xlfn.XLOOKUP($C42,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E42" s="105" t="str">
+      <c r="E42" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F42" s="96" t="str">
+      <c r="F42" s="117" t="str">
         <f t="array" ref="F42">IF(COUNTIF(C$2:C42,C42)&gt;1, ROW()-MAX(IF(C$1:C41=C42,ROW(C$1:C41)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G42" s="96" t="str">
+      <c r="G42" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H42" s="96" t="str">
+      <c r="H42" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I42" s="96"/>
+      <c r="I42" s="117"/>
     </row>
     <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="94">
+      <c r="A43" s="119">
         <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="B43" s="94" t="str">
+      <c r="B43" s="119" t="str">
         <f>_xlfn.XLOOKUP($C43,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C43" s="95"/>
-      <c r="D43" s="94">
+      <c r="C43" s="108"/>
+      <c r="D43" s="119">
         <f>_xlfn.XLOOKUP($C43,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E43" s="105" t="str">
+      <c r="E43" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F43" s="96" t="str">
+      <c r="F43" s="117" t="str">
         <f t="array" ref="F43">IF(COUNTIF(C$2:C43,C43)&gt;1, ROW()-MAX(IF(C$1:C42=C43,ROW(C$1:C42)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G43" s="96" t="str">
+      <c r="G43" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H43" s="96" t="str">
+      <c r="H43" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I43" s="96"/>
+      <c r="I43" s="117"/>
     </row>
     <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="94">
+      <c r="A44" s="119">
         <f t="shared" si="5"/>
         <v>43</v>
       </c>
-      <c r="B44" s="94" t="str">
+      <c r="B44" s="119" t="str">
         <f>_xlfn.XLOOKUP($C44,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C44" s="95"/>
-      <c r="D44" s="94">
+      <c r="C44" s="108"/>
+      <c r="D44" s="119">
         <f>_xlfn.XLOOKUP($C44,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E44" s="105" t="str">
+      <c r="E44" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F44" s="96" t="str">
+      <c r="F44" s="117" t="str">
         <f t="array" ref="F44">IF(COUNTIF(C$2:C44,C44)&gt;1, ROW()-MAX(IF(C$1:C43=C44,ROW(C$1:C43)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G44" s="96" t="str">
+      <c r="G44" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H44" s="96" t="str">
+      <c r="H44" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I44" s="96"/>
+      <c r="I44" s="117"/>
     </row>
     <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="94">
+      <c r="A45" s="119">
         <f t="shared" si="5"/>
         <v>44</v>
       </c>
-      <c r="B45" s="94" t="str">
+      <c r="B45" s="119" t="str">
         <f>_xlfn.XLOOKUP($C45,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C45" s="95"/>
-      <c r="D45" s="94">
+      <c r="C45" s="108"/>
+      <c r="D45" s="119">
         <f>_xlfn.XLOOKUP($C45,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E45" s="105" t="str">
+      <c r="E45" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F45" s="96" t="str">
+      <c r="F45" s="117" t="str">
         <f t="array" ref="F45">IF(COUNTIF(C$2:C45,C45)&gt;1, ROW()-MAX(IF(C$1:C44=C45,ROW(C$1:C44)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G45" s="96" t="str">
+      <c r="G45" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H45" s="96" t="str">
+      <c r="H45" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I45" s="96"/>
+      <c r="I45" s="117"/>
     </row>
     <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="94">
+      <c r="A46" s="119">
         <f t="shared" si="5"/>
         <v>45</v>
       </c>
-      <c r="B46" s="94" t="str">
+      <c r="B46" s="119" t="str">
         <f>_xlfn.XLOOKUP($C46,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C46" s="95"/>
-      <c r="D46" s="94">
+      <c r="C46" s="108"/>
+      <c r="D46" s="119">
         <f>_xlfn.XLOOKUP($C46,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E46" s="105" t="str">
+      <c r="E46" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F46" s="96" t="str">
+      <c r="F46" s="117" t="str">
         <f t="array" ref="F46">IF(COUNTIF(C$2:C46,C46)&gt;1, ROW()-MAX(IF(C$1:C45=C46,ROW(C$1:C45)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G46" s="96" t="str">
+      <c r="G46" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H46" s="96" t="str">
+      <c r="H46" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I46" s="96"/>
+      <c r="I46" s="117"/>
     </row>
     <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="94">
+      <c r="A47" s="119">
         <f t="shared" si="5"/>
         <v>46</v>
       </c>
-      <c r="B47" s="94" t="str">
+      <c r="B47" s="119" t="str">
         <f>_xlfn.XLOOKUP($C47,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C47" s="95"/>
-      <c r="D47" s="94">
+      <c r="C47" s="108"/>
+      <c r="D47" s="119">
         <f>_xlfn.XLOOKUP($C47,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E47" s="105" t="str">
+      <c r="E47" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F47" s="96" t="str">
+      <c r="F47" s="117" t="str">
         <f t="array" ref="F47">IF(COUNTIF(C$2:C47,C47)&gt;1, ROW()-MAX(IF(C$1:C46=C47,ROW(C$1:C46)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G47" s="96" t="str">
+      <c r="G47" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H47" s="96" t="str">
+      <c r="H47" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I47" s="96"/>
+      <c r="I47" s="117"/>
     </row>
     <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="94">
+      <c r="A48" s="119">
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="B48" s="94" t="str">
+      <c r="B48" s="119" t="str">
         <f>_xlfn.XLOOKUP($C48,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C48" s="95"/>
-      <c r="D48" s="94">
+      <c r="C48" s="108"/>
+      <c r="D48" s="119">
         <f>_xlfn.XLOOKUP($C48,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E48" s="105" t="str">
+      <c r="E48" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F48" s="96" t="str">
+      <c r="F48" s="117" t="str">
         <f t="array" ref="F48">IF(COUNTIF(C$2:C48,C48)&gt;1, ROW()-MAX(IF(C$1:C47=C48,ROW(C$1:C47)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G48" s="96" t="str">
+      <c r="G48" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H48" s="96" t="str">
+      <c r="H48" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I48" s="96"/>
+      <c r="I48" s="117"/>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="94">
+      <c r="A49" s="119">
         <f t="shared" si="5"/>
         <v>48</v>
       </c>
-      <c r="B49" s="94" t="str">
+      <c r="B49" s="119" t="str">
         <f>_xlfn.XLOOKUP($C49,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C49" s="95"/>
-      <c r="D49" s="94">
+      <c r="C49" s="108"/>
+      <c r="D49" s="119">
         <f>_xlfn.XLOOKUP($C49,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E49" s="105" t="str">
+      <c r="E49" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F49" s="96" t="str">
+      <c r="F49" s="117" t="str">
         <f t="array" ref="F49">IF(COUNTIF(C$2:C49,C49)&gt;1, ROW()-MAX(IF(C$1:C48=C49,ROW(C$1:C48)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G49" s="96" t="str">
+      <c r="G49" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H49" s="96" t="str">
+      <c r="H49" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I49" s="96"/>
+      <c r="I49" s="117"/>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="94">
+      <c r="A50" s="119">
         <f t="shared" si="5"/>
         <v>49</v>
       </c>
-      <c r="B50" s="94" t="str">
+      <c r="B50" s="119" t="str">
         <f>_xlfn.XLOOKUP($C50,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C50" s="95"/>
-      <c r="D50" s="94">
+      <c r="C50" s="108"/>
+      <c r="D50" s="119">
         <f>_xlfn.XLOOKUP($C50,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E50" s="105" t="str">
+      <c r="E50" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F50" s="96" t="str">
+      <c r="F50" s="117" t="str">
         <f t="array" ref="F50">IF(COUNTIF(C$2:C50,C50)&gt;1, ROW()-MAX(IF(C$1:C49=C50,ROW(C$1:C49)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G50" s="96" t="str">
+      <c r="G50" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H50" s="96" t="str">
+      <c r="H50" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I50" s="96"/>
+      <c r="I50" s="117"/>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="94">
+      <c r="A51" s="119">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="B51" s="94" t="str">
+      <c r="B51" s="119" t="str">
         <f>_xlfn.XLOOKUP($C51,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C51" s="95"/>
-      <c r="D51" s="94">
+      <c r="C51" s="108"/>
+      <c r="D51" s="119">
         <f>_xlfn.XLOOKUP($C51,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E51" s="105" t="str">
+      <c r="E51" s="116" t="str">
         <f t="shared" si="6"/>
         <v>〿相邻3次</v>
       </c>
-      <c r="F51" s="96" t="str">
+      <c r="F51" s="117" t="str">
         <f t="array" ref="F51">IF(COUNTIF(C$2:C51,C51)&gt;1, ROW()-MAX(IF(C$1:C50=C51,ROW(C$1:C50)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G51" s="96" t="str">
+      <c r="G51" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H51" s="96" t="str">
+      <c r="H51" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I51" s="96"/>
+      <c r="I51" s="117"/>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="94">
+      <c r="A52" s="119">
         <f t="shared" si="5"/>
         <v>51</v>
       </c>
-      <c r="B52" s="94" t="str">
+      <c r="B52" s="119" t="str">
         <f>_xlfn.XLOOKUP($C52,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v>表演</v>
       </c>
-      <c r="C52" s="95"/>
-      <c r="D52" s="94">
+      <c r="C52" s="108"/>
+      <c r="D52" s="119">
         <f>_xlfn.XLOOKUP($C52,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v>0</v>
       </c>
-      <c r="E52" s="105" t="str">
+      <c r="E52" s="116" t="str">
         <f t="shared" si="6"/>
         <v>OK</v>
       </c>
-      <c r="F52" s="96" t="str">
+      <c r="F52" s="117" t="str">
         <f t="array" ref="F52">IF(COUNTIF(C$2:C52,C52)&gt;1, ROW()-MAX(IF(C$1:C51=C52,ROW(C$1:C51)))-1, "首次")</f>
         <v>首次</v>
       </c>
-      <c r="G52" s="96" t="str">
+      <c r="G52" s="117" t="str">
         <f t="shared" si="7"/>
         <v>⚠️同节奏</v>
       </c>
-      <c r="H52" s="96" t="str">
+      <c r="H52" s="117" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="I52" s="96"/>
+      <c r="I52" s="117"/>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="96"/>
-      <c r="B53" s="96"/>
-      <c r="C53" s="96"/>
-      <c r="D53" s="96"/>
-      <c r="E53" s="96"/>
-      <c r="F53" s="96"/>
-      <c r="G53" s="96"/>
-      <c r="H53" s="96"/>
-      <c r="I53" s="96"/>
+      <c r="A53" s="117"/>
+      <c r="B53" s="117"/>
+      <c r="C53" s="107"/>
+      <c r="D53" s="117"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="117"/>
+      <c r="H53" s="117"/>
+      <c r="I53" s="117"/>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="96"/>
-      <c r="B54" s="96"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="96"/>
-      <c r="E54" s="96"/>
-      <c r="F54" s="96"/>
-      <c r="G54" s="96"/>
-      <c r="H54" s="96"/>
-      <c r="I54" s="96"/>
+      <c r="A54" s="117"/>
+      <c r="B54" s="117"/>
+      <c r="C54" s="107"/>
+      <c r="D54" s="117"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="117"/>
+      <c r="H54" s="117"/>
+      <c r="I54" s="117"/>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="96"/>
-      <c r="B55" s="96"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="96"/>
-      <c r="E55" s="96"/>
-      <c r="F55" s="96"/>
-      <c r="G55" s="96"/>
-      <c r="H55" s="96"/>
-      <c r="I55" s="96"/>
+      <c r="A55" s="117"/>
+      <c r="B55" s="117"/>
+      <c r="C55" s="107"/>
+      <c r="D55" s="117"/>
+      <c r="E55" s="117"/>
+      <c r="F55" s="117"/>
+      <c r="G55" s="117"/>
+      <c r="H55" s="117"/>
+      <c r="I55" s="117"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:I52">
     <cfRule type="expression" dxfId="23" priority="7">
@@ -5523,1953 +5648,1954 @@
   <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.46484375" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.46484375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="50.3984375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.53125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="9.06640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
-    <col min="10" max="10" width="9.06640625" style="116" customWidth="1"/>
+    <col min="1" max="1" width="9.46484375" style="80" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.46484375" style="80" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" style="80" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="80" customWidth="1"/>
+    <col min="5" max="5" width="50.3984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.53125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.06640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9.06640625" style="64" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="68" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="81" t="s">
         <v>184</v>
       </c>
-      <c r="G1" s="73" t="s">
+      <c r="G1" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="H1" s="73" t="s">
+      <c r="H1" s="83" t="s">
         <v>186</v>
       </c>
-      <c r="I1" s="77">
+      <c r="I1" s="84">
         <v>0.8125</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="85" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
+      <c r="A2" s="69">
         <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="str">
+      <c r="B2" s="69" t="str">
         <f>_xlfn.XLOOKUP($C2,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C2" s="15" t="str">
+      <c r="C2" s="70" t="str">
         <f t="array" ref="C2">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E2)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="71" t="str">
         <f>_xlfn.XLOOKUP($C2,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="74">
-        <v>0</v>
-      </c>
-      <c r="H2" s="75">
+      <c r="E2" s="87"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="89">
+        <v>0</v>
+      </c>
+      <c r="H2" s="90">
         <v>3</v>
       </c>
-      <c r="I2" s="76">
+      <c r="I2" s="91">
         <f t="shared" ref="I2:I33" si="1">$I1+TIME(0,0,15)+$F2</f>
         <v>0.81267361111111114</v>
       </c>
-      <c r="J2" s="65" t="e">
+      <c r="J2" s="92" t="e">
         <f t="shared" ref="J2:J33" si="2">"ren """ &amp; E2 &amp; """ """ &amp; TEXT(ROW(A1),"00") &amp; "-" &amp; LEFT(E2,FIND(".",E2)-1) &amp; MID(E2,FIND(".",E2),LEN(E2)) &amp; """"</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+      <c r="A3" s="69">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="str">
+      <c r="B3" s="69" t="str">
         <f>_xlfn.XLOOKUP($C3,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C3" s="15" t="str">
+      <c r="C3" s="70" t="str">
         <f t="array" ref="C3">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E3)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D3" s="5" t="str">
+      <c r="D3" s="71" t="str">
         <f>_xlfn.XLOOKUP($C3,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="74">
-        <v>0</v>
-      </c>
-      <c r="H3" s="75">
+      <c r="E3" s="87"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="89">
+        <v>0</v>
+      </c>
+      <c r="H3" s="90">
         <v>3</v>
       </c>
-      <c r="I3" s="76">
+      <c r="I3" s="91">
         <f t="shared" si="1"/>
         <v>0.81284722222222228</v>
       </c>
-      <c r="J3" s="65" t="e">
+      <c r="J3" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="A4" s="69">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="str">
+      <c r="B4" s="69" t="str">
         <f>_xlfn.XLOOKUP($C4,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C4" s="15" t="str">
+      <c r="C4" s="70" t="str">
         <f t="array" ref="C4">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E4)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D4" s="5" t="str">
+      <c r="D4" s="71" t="str">
         <f>_xlfn.XLOOKUP($C4,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="74">
-        <v>0</v>
-      </c>
-      <c r="H4" s="75">
+      <c r="E4" s="87"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="89">
+        <v>0</v>
+      </c>
+      <c r="H4" s="90">
         <v>3</v>
       </c>
-      <c r="I4" s="76">
+      <c r="I4" s="91">
         <f t="shared" si="1"/>
         <v>0.81302083333333341</v>
       </c>
-      <c r="J4" s="65" t="e">
+      <c r="J4" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="A5" s="69">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="str">
+      <c r="B5" s="69" t="str">
         <f>_xlfn.XLOOKUP($C5,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C5" s="15" t="str">
+      <c r="C5" s="70" t="str">
         <f t="array" ref="C5">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E5)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D5" s="5" t="str">
+      <c r="D5" s="71" t="str">
         <f>_xlfn.XLOOKUP($C5,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="74">
-        <v>0</v>
-      </c>
-      <c r="H5" s="75">
+      <c r="E5" s="87"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="89">
+        <v>0</v>
+      </c>
+      <c r="H5" s="90">
         <v>3</v>
       </c>
-      <c r="I5" s="76">
+      <c r="I5" s="91">
         <f t="shared" si="1"/>
         <v>0.81319444444444455</v>
       </c>
-      <c r="J5" s="65" t="e">
+      <c r="J5" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="A6" s="69">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="str">
+      <c r="B6" s="69" t="str">
         <f>_xlfn.XLOOKUP($C6,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C6" s="15" t="str">
+      <c r="C6" s="70" t="str">
         <f t="array" ref="C6">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E6)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D6" s="5" t="str">
+      <c r="D6" s="71" t="str">
         <f>_xlfn.XLOOKUP($C6,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="74">
-        <v>0</v>
-      </c>
-      <c r="H6" s="75">
+      <c r="E6" s="86"/>
+      <c r="F6" s="88"/>
+      <c r="G6" s="89">
+        <v>0</v>
+      </c>
+      <c r="H6" s="90">
         <v>3</v>
       </c>
-      <c r="I6" s="76">
+      <c r="I6" s="91">
         <f t="shared" si="1"/>
         <v>0.81336805555555569</v>
       </c>
-      <c r="J6" s="65" t="e">
+      <c r="J6" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="A7" s="69">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="str">
+      <c r="B7" s="69" t="str">
         <f>_xlfn.XLOOKUP($C7,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C7" s="15" t="str">
+      <c r="C7" s="70" t="str">
         <f t="array" ref="C7">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E7)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D7" s="5" t="str">
+      <c r="D7" s="71" t="str">
         <f>_xlfn.XLOOKUP($C7,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="74">
-        <v>0</v>
-      </c>
-      <c r="H7" s="75">
+      <c r="E7" s="87"/>
+      <c r="F7" s="88"/>
+      <c r="G7" s="89">
+        <v>0</v>
+      </c>
+      <c r="H7" s="90">
         <v>3</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="91">
         <f t="shared" si="1"/>
         <v>0.81354166666666683</v>
       </c>
-      <c r="J7" s="65" t="e">
+      <c r="J7" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="A8" s="69">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="str">
+      <c r="B8" s="69" t="str">
         <f>_xlfn.XLOOKUP($C8,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C8" s="15" t="str">
+      <c r="C8" s="70" t="str">
         <f t="array" ref="C8">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E8)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D8" s="5" t="str">
+      <c r="D8" s="71" t="str">
         <f>_xlfn.XLOOKUP($C8,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="74">
-        <v>0</v>
-      </c>
-      <c r="H8" s="75">
+      <c r="E8" s="87"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="89">
+        <v>0</v>
+      </c>
+      <c r="H8" s="90">
         <v>3</v>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="91">
         <f t="shared" si="1"/>
         <v>0.81371527777777797</v>
       </c>
-      <c r="J8" s="65" t="e">
+      <c r="J8" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="A9" s="69">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="str">
+      <c r="B9" s="69" t="str">
         <f>_xlfn.XLOOKUP($C9,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C9" s="15" t="str">
+      <c r="C9" s="70" t="str">
         <f t="array" ref="C9">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E9)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D9" s="8" t="str">
+      <c r="D9" s="72" t="str">
         <f>_xlfn.XLOOKUP($C9,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="74">
-        <v>0</v>
-      </c>
-      <c r="H9" s="75">
+      <c r="E9" s="86"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="89">
+        <v>0</v>
+      </c>
+      <c r="H9" s="90">
         <v>3</v>
       </c>
-      <c r="I9" s="76">
+      <c r="I9" s="91">
         <f t="shared" si="1"/>
         <v>0.81388888888888911</v>
       </c>
-      <c r="J9" s="65" t="e">
+      <c r="J9" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="A10" s="69">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="str">
+      <c r="B10" s="69" t="str">
         <f>_xlfn.XLOOKUP($C10,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C10" s="15" t="str">
+      <c r="C10" s="70" t="str">
         <f t="array" ref="C10">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E10)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D10" s="5" t="str">
+      <c r="D10" s="71" t="str">
         <f>_xlfn.XLOOKUP($C10,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="74">
-        <v>0</v>
-      </c>
-      <c r="H10" s="75">
+      <c r="E10" s="87"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="89">
+        <v>0</v>
+      </c>
+      <c r="H10" s="90">
         <v>3</v>
       </c>
-      <c r="I10" s="76">
+      <c r="I10" s="91">
         <f t="shared" si="1"/>
         <v>0.81406250000000024</v>
       </c>
-      <c r="J10" s="65" t="e">
+      <c r="J10" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+      <c r="A11" s="69">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="str">
+      <c r="B11" s="69" t="str">
         <f>_xlfn.XLOOKUP($C11,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C11" s="15" t="str">
+      <c r="C11" s="70" t="str">
         <f t="array" ref="C11">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E11)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D11" s="5" t="str">
+      <c r="D11" s="71" t="str">
         <f>_xlfn.XLOOKUP($C11,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="74">
-        <v>0</v>
-      </c>
-      <c r="H11" s="75">
+      <c r="E11" s="87"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="89">
+        <v>0</v>
+      </c>
+      <c r="H11" s="90">
         <v>3</v>
       </c>
-      <c r="I11" s="76">
+      <c r="I11" s="91">
         <f t="shared" si="1"/>
         <v>0.81423611111111138</v>
       </c>
-      <c r="J11" s="65" t="e">
+      <c r="J11" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+      <c r="A12" s="69">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="str">
+      <c r="B12" s="69" t="str">
         <f>_xlfn.XLOOKUP($C12,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C12" s="15" t="str">
+      <c r="C12" s="70" t="str">
         <f t="array" ref="C12">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E12)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D12" s="5" t="str">
+      <c r="D12" s="71" t="str">
         <f>_xlfn.XLOOKUP($C12,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="74">
-        <v>0</v>
-      </c>
-      <c r="H12" s="75">
+      <c r="E12" s="86"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="89">
+        <v>0</v>
+      </c>
+      <c r="H12" s="90">
         <v>3</v>
       </c>
-      <c r="I12" s="76">
+      <c r="I12" s="91">
         <f t="shared" si="1"/>
         <v>0.81440972222222252</v>
       </c>
-      <c r="J12" s="65" t="e">
+      <c r="J12" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+      <c r="A13" s="69">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="str">
+      <c r="B13" s="69" t="str">
         <f>_xlfn.XLOOKUP($C13,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C13" s="15" t="str">
+      <c r="C13" s="70" t="str">
         <f t="array" ref="C13">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E13)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D13" s="8" t="str">
+      <c r="D13" s="72" t="str">
         <f>_xlfn.XLOOKUP($C13,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="74">
-        <v>0</v>
-      </c>
-      <c r="H13" s="75">
+      <c r="E13" s="86"/>
+      <c r="F13" s="88"/>
+      <c r="G13" s="89">
+        <v>0</v>
+      </c>
+      <c r="H13" s="90">
         <v>3</v>
       </c>
-      <c r="I13" s="76">
+      <c r="I13" s="91">
         <f t="shared" si="1"/>
         <v>0.81458333333333366</v>
       </c>
-      <c r="J13" s="65" t="e">
+      <c r="J13" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+      <c r="A14" s="69">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="str">
+      <c r="B14" s="69" t="str">
         <f>_xlfn.XLOOKUP($C14,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C14" s="15" t="str">
+      <c r="C14" s="70" t="str">
         <f t="array" ref="C14">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E14)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="D14" s="73" t="str">
         <f>_xlfn.XLOOKUP($C14,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="74">
-        <v>0</v>
-      </c>
-      <c r="H14" s="75">
+      <c r="E14" s="87"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="89">
+        <v>0</v>
+      </c>
+      <c r="H14" s="90">
         <v>3</v>
       </c>
-      <c r="I14" s="76">
+      <c r="I14" s="91">
         <f t="shared" si="1"/>
         <v>0.8147569444444448</v>
       </c>
-      <c r="J14" s="65" t="e">
+      <c r="J14" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+      <c r="A15" s="69">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="str">
+      <c r="B15" s="69" t="str">
         <f>_xlfn.XLOOKUP($C15,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C15" s="15" t="str">
+      <c r="C15" s="70" t="str">
         <f t="array" ref="C15">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E15)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D15" s="5" t="str">
+      <c r="D15" s="71" t="str">
         <f>_xlfn.XLOOKUP($C15,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="74">
-        <v>0</v>
-      </c>
-      <c r="H15" s="75">
+      <c r="E15" s="87"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="89">
+        <v>0</v>
+      </c>
+      <c r="H15" s="90">
         <v>3</v>
       </c>
-      <c r="I15" s="76">
+      <c r="I15" s="91">
         <f t="shared" si="1"/>
         <v>0.81493055555555594</v>
       </c>
-      <c r="J15" s="65" t="e">
+      <c r="J15" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
+      <c r="A16" s="69">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="str">
+      <c r="B16" s="69" t="str">
         <f>_xlfn.XLOOKUP($C16,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C16" s="15" t="str">
+      <c r="C16" s="70" t="str">
         <f t="array" ref="C16">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E16)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D16" s="8" t="str">
+      <c r="D16" s="72" t="str">
         <f>_xlfn.XLOOKUP($C16,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="74">
-        <v>0</v>
-      </c>
-      <c r="H16" s="75">
+      <c r="E16" s="86"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="89">
+        <v>0</v>
+      </c>
+      <c r="H16" s="90">
         <v>3</v>
       </c>
-      <c r="I16" s="76">
+      <c r="I16" s="91">
         <f t="shared" si="1"/>
         <v>0.81510416666666707</v>
       </c>
-      <c r="J16" s="65" t="e">
+      <c r="J16" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+      <c r="A17" s="69">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="str">
+      <c r="B17" s="69" t="str">
         <f>_xlfn.XLOOKUP($C17,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C17" s="15" t="str">
+      <c r="C17" s="70" t="str">
         <f t="array" ref="C17">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E17)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D17" s="5" t="str">
+      <c r="D17" s="71" t="str">
         <f>_xlfn.XLOOKUP($C17,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="74">
-        <v>0</v>
-      </c>
-      <c r="H17" s="75">
+      <c r="E17" s="87"/>
+      <c r="F17" s="88"/>
+      <c r="G17" s="89">
+        <v>0</v>
+      </c>
+      <c r="H17" s="90">
         <v>3</v>
       </c>
-      <c r="I17" s="76">
+      <c r="I17" s="91">
         <f t="shared" si="1"/>
         <v>0.81527777777777821</v>
       </c>
-      <c r="J17" s="65" t="e">
+      <c r="J17" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+      <c r="A18" s="69">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="str">
+      <c r="B18" s="69" t="str">
         <f>_xlfn.XLOOKUP($C18,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C18" s="15" t="str">
+      <c r="C18" s="70" t="str">
         <f t="array" ref="C18">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E18)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D18" s="5" t="str">
+      <c r="D18" s="71" t="str">
         <f>_xlfn.XLOOKUP($C18,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="74">
-        <v>0</v>
-      </c>
-      <c r="H18" s="75">
+      <c r="E18" s="87"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="89">
+        <v>0</v>
+      </c>
+      <c r="H18" s="90">
         <v>3</v>
       </c>
-      <c r="I18" s="76">
+      <c r="I18" s="91">
         <f t="shared" si="1"/>
         <v>0.81545138888888935</v>
       </c>
-      <c r="J18" s="65" t="e">
+      <c r="J18" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+      <c r="A19" s="69">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="str">
+      <c r="B19" s="69" t="str">
         <f>_xlfn.XLOOKUP($C19,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C19" s="15" t="str">
+      <c r="C19" s="70" t="str">
         <f t="array" ref="C19">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E19)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D19" s="5" t="str">
+      <c r="D19" s="71" t="str">
         <f>_xlfn.XLOOKUP($C19,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="74">
-        <v>0</v>
-      </c>
-      <c r="H19" s="75">
+      <c r="E19" s="86"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="89">
+        <v>0</v>
+      </c>
+      <c r="H19" s="90">
         <v>3</v>
       </c>
-      <c r="I19" s="76">
+      <c r="I19" s="91">
         <f t="shared" si="1"/>
         <v>0.81562500000000049</v>
       </c>
-      <c r="J19" s="65" t="e">
+      <c r="J19" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+      <c r="A20" s="69">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="str">
+      <c r="B20" s="69" t="str">
         <f>_xlfn.XLOOKUP($C20,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C20" s="15" t="str">
+      <c r="C20" s="70" t="str">
         <f t="array" ref="C20">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E20)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D20" s="5" t="str">
+      <c r="D20" s="71" t="str">
         <f>_xlfn.XLOOKUP($C20,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E20" s="4"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="74">
-        <v>0</v>
-      </c>
-      <c r="H20" s="75">
+      <c r="E20" s="86"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="89">
+        <v>0</v>
+      </c>
+      <c r="H20" s="90">
         <v>3</v>
       </c>
-      <c r="I20" s="76">
+      <c r="I20" s="91">
         <f t="shared" si="1"/>
         <v>0.81579861111111163</v>
       </c>
-      <c r="J20" s="65" t="e">
+      <c r="J20" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
+      <c r="A21" s="69">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="str">
+      <c r="B21" s="69" t="str">
         <f>_xlfn.XLOOKUP($C21,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C21" s="15" t="str">
+      <c r="C21" s="70" t="str">
         <f t="array" ref="C21">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E21)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D21" s="5" t="str">
+      <c r="D21" s="71" t="str">
         <f>_xlfn.XLOOKUP($C21,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="74">
-        <v>0</v>
-      </c>
-      <c r="H21" s="75">
+      <c r="E21" s="87"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="89">
+        <v>0</v>
+      </c>
+      <c r="H21" s="90">
         <v>3</v>
       </c>
-      <c r="I21" s="76">
+      <c r="I21" s="91">
         <f t="shared" si="1"/>
         <v>0.81597222222222276</v>
       </c>
-      <c r="J21" s="65" t="e">
+      <c r="J21" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+      <c r="A22" s="69">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="str">
+      <c r="B22" s="69" t="str">
         <f>_xlfn.XLOOKUP($C22,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C22" s="15" t="str">
+      <c r="C22" s="70" t="str">
         <f t="array" ref="C22">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E22)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D22" s="5" t="str">
+      <c r="D22" s="71" t="str">
         <f>_xlfn.XLOOKUP($C22,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="74">
-        <v>0</v>
-      </c>
-      <c r="H22" s="75">
+      <c r="E22" s="87"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="89">
+        <v>0</v>
+      </c>
+      <c r="H22" s="90">
         <v>3</v>
       </c>
-      <c r="I22" s="76">
+      <c r="I22" s="91">
         <f t="shared" si="1"/>
         <v>0.8161458333333339</v>
       </c>
-      <c r="J22" s="65" t="e">
+      <c r="J22" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+      <c r="A23" s="69">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="str">
+      <c r="B23" s="69" t="str">
         <f>_xlfn.XLOOKUP($C23,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C23" s="15" t="str">
+      <c r="C23" s="70" t="str">
         <f t="array" ref="C23">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E23)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D23" s="5" t="str">
+      <c r="D23" s="71" t="str">
         <f>_xlfn.XLOOKUP($C23,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="74">
-        <v>0</v>
-      </c>
-      <c r="H23" s="75">
+      <c r="E23" s="86"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="89">
+        <v>0</v>
+      </c>
+      <c r="H23" s="90">
         <v>3</v>
       </c>
-      <c r="I23" s="76">
+      <c r="I23" s="91">
         <f t="shared" si="1"/>
         <v>0.81631944444444504</v>
       </c>
-      <c r="J23" s="65" t="e">
+      <c r="J23" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
+      <c r="A24" s="69">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="str">
+      <c r="B24" s="69" t="str">
         <f>_xlfn.XLOOKUP($C24,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C24" s="15" t="str">
+      <c r="C24" s="70" t="str">
         <f t="array" ref="C24">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E24)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D24" s="7" t="str">
+      <c r="D24" s="73" t="str">
         <f>_xlfn.XLOOKUP($C24,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E24" s="4"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="74">
-        <v>0</v>
-      </c>
-      <c r="H24" s="75">
+      <c r="E24" s="86"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="89">
+        <v>0</v>
+      </c>
+      <c r="H24" s="90">
         <v>3</v>
       </c>
-      <c r="I24" s="76">
+      <c r="I24" s="91">
         <f t="shared" si="1"/>
         <v>0.81649305555555618</v>
       </c>
-      <c r="J24" s="65" t="e">
+      <c r="J24" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A25" s="4">
+      <c r="A25" s="69">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="str">
+      <c r="B25" s="69" t="str">
         <f>_xlfn.XLOOKUP($C25,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C25" s="15" t="str">
+      <c r="C25" s="70" t="str">
         <f t="array" ref="C25">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E25)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D25" s="7" t="str">
+      <c r="D25" s="73" t="str">
         <f>_xlfn.XLOOKUP($C25,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="74">
-        <v>0</v>
-      </c>
-      <c r="H25" s="75">
+      <c r="E25" s="86"/>
+      <c r="F25" s="88"/>
+      <c r="G25" s="89">
+        <v>0</v>
+      </c>
+      <c r="H25" s="90">
         <v>3</v>
       </c>
-      <c r="I25" s="76">
+      <c r="I25" s="91">
         <f t="shared" si="1"/>
         <v>0.81666666666666732</v>
       </c>
-      <c r="J25" s="65" t="e">
+      <c r="J25" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A26" s="4">
+      <c r="A26" s="69">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="str">
+      <c r="B26" s="69" t="str">
         <f>_xlfn.XLOOKUP($C26,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C26" s="15" t="str">
+      <c r="C26" s="70" t="str">
         <f t="array" ref="C26">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E26)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D26" s="5" t="str">
+      <c r="D26" s="71" t="str">
         <f>_xlfn.XLOOKUP($C26,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="74">
-        <v>0</v>
-      </c>
-      <c r="H26" s="75">
+      <c r="E26" s="86"/>
+      <c r="F26" s="88"/>
+      <c r="G26" s="89">
+        <v>0</v>
+      </c>
+      <c r="H26" s="90">
         <v>3</v>
       </c>
-      <c r="I26" s="76">
+      <c r="I26" s="91">
         <f t="shared" si="1"/>
         <v>0.81684027777777846</v>
       </c>
-      <c r="J26" s="65" t="e">
+      <c r="J26" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A27" s="4">
+      <c r="A27" s="69">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="str">
+      <c r="B27" s="69" t="str">
         <f>_xlfn.XLOOKUP($C27,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C27" s="15" t="str">
+      <c r="C27" s="70" t="str">
         <f t="array" ref="C27">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E27)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D27" s="5" t="str">
+      <c r="D27" s="71" t="str">
         <f>_xlfn.XLOOKUP($C27,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="74">
-        <v>0</v>
-      </c>
-      <c r="H27" s="75">
+      <c r="E27" s="86"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="89">
+        <v>0</v>
+      </c>
+      <c r="H27" s="90">
         <v>3</v>
       </c>
-      <c r="I27" s="76">
+      <c r="I27" s="91">
         <f t="shared" si="1"/>
         <v>0.81701388888888959</v>
       </c>
-      <c r="J27" s="65" t="e">
+      <c r="J27" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
+      <c r="A28" s="69">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="str">
+      <c r="B28" s="69" t="str">
         <f>_xlfn.XLOOKUP($C28,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C28" s="15" t="str">
+      <c r="C28" s="70" t="str">
         <f t="array" ref="C28">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E28)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D28" s="5" t="str">
+      <c r="D28" s="71" t="str">
         <f>_xlfn.XLOOKUP($C28,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="74">
-        <v>0</v>
-      </c>
-      <c r="H28" s="75">
+      <c r="E28" s="86"/>
+      <c r="F28" s="88"/>
+      <c r="G28" s="89">
+        <v>0</v>
+      </c>
+      <c r="H28" s="90">
         <v>3</v>
       </c>
-      <c r="I28" s="76">
+      <c r="I28" s="91">
         <f t="shared" si="1"/>
         <v>0.81718750000000073</v>
       </c>
-      <c r="J28" s="65" t="e">
+      <c r="J28" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
+      <c r="A29" s="69">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="str">
+      <c r="B29" s="69" t="str">
         <f>_xlfn.XLOOKUP($C29,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C29" s="15" t="str">
+      <c r="C29" s="70" t="str">
         <f t="array" ref="C29">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E29)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D29" s="8" t="str">
+      <c r="D29" s="72" t="str">
         <f>_xlfn.XLOOKUP($C29,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="74">
-        <v>0</v>
-      </c>
-      <c r="H29" s="75">
+      <c r="E29" s="87"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="89">
+        <v>0</v>
+      </c>
+      <c r="H29" s="90">
         <v>3</v>
       </c>
-      <c r="I29" s="76">
+      <c r="I29" s="91">
         <f t="shared" si="1"/>
         <v>0.81736111111111187</v>
       </c>
-      <c r="J29" s="65" t="e">
+      <c r="J29" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
+      <c r="A30" s="69">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="str">
+      <c r="B30" s="69" t="str">
         <f>_xlfn.XLOOKUP($C30,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C30" s="15" t="str">
+      <c r="C30" s="70" t="str">
         <f t="array" ref="C30">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E30)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D30" s="5" t="str">
+      <c r="D30" s="71" t="str">
         <f>_xlfn.XLOOKUP($C30,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="62"/>
-      <c r="G30" s="74">
-        <v>0</v>
-      </c>
-      <c r="H30" s="75">
+      <c r="E30" s="86"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="89">
+        <v>0</v>
+      </c>
+      <c r="H30" s="90">
         <v>3</v>
       </c>
-      <c r="I30" s="76">
+      <c r="I30" s="91">
         <f t="shared" si="1"/>
         <v>0.81753472222222301</v>
       </c>
-      <c r="J30" s="65" t="e">
+      <c r="J30" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A31" s="4">
+      <c r="A31" s="69">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="str">
+      <c r="B31" s="69" t="str">
         <f>_xlfn.XLOOKUP($C31,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C31" s="15" t="str">
+      <c r="C31" s="70" t="str">
         <f t="array" ref="C31">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E31)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D31" s="5" t="str">
+      <c r="D31" s="71" t="str">
         <f>_xlfn.XLOOKUP($C31,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="74">
-        <v>0</v>
-      </c>
-      <c r="H31" s="75">
+      <c r="E31" s="86"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="89">
+        <v>0</v>
+      </c>
+      <c r="H31" s="90">
         <v>3</v>
       </c>
-      <c r="I31" s="76">
+      <c r="I31" s="91">
         <f t="shared" si="1"/>
         <v>0.81770833333333415</v>
       </c>
-      <c r="J31" s="65" t="e">
+      <c r="J31" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
+      <c r="A32" s="69">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="str">
+      <c r="B32" s="69" t="str">
         <f>_xlfn.XLOOKUP($C32,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C32" s="15" t="str">
+      <c r="C32" s="70" t="str">
         <f t="array" ref="C32">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E32)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D32" s="5" t="str">
+      <c r="D32" s="71" t="str">
         <f>_xlfn.XLOOKUP($C32,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="62"/>
-      <c r="G32" s="74">
-        <v>0</v>
-      </c>
-      <c r="H32" s="75">
+      <c r="E32" s="86"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="89">
+        <v>0</v>
+      </c>
+      <c r="H32" s="90">
         <v>3</v>
       </c>
-      <c r="I32" s="76">
+      <c r="I32" s="91">
         <f t="shared" si="1"/>
         <v>0.81788194444444529</v>
       </c>
-      <c r="J32" s="65" t="e">
+      <c r="J32" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
+      <c r="A33" s="69">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="str">
+      <c r="B33" s="69" t="str">
         <f>_xlfn.XLOOKUP($C33,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C33" s="15" t="str">
+      <c r="C33" s="70" t="str">
         <f t="array" ref="C33">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E33)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D33" s="10" t="str">
+      <c r="D33" s="74" t="str">
         <f>_xlfn.XLOOKUP($C33,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="62"/>
-      <c r="G33" s="74">
-        <v>0</v>
-      </c>
-      <c r="H33" s="75">
+      <c r="E33" s="86"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="89">
+        <v>0</v>
+      </c>
+      <c r="H33" s="90">
         <v>3</v>
       </c>
-      <c r="I33" s="76">
+      <c r="I33" s="91">
         <f t="shared" si="1"/>
         <v>0.81805555555555642</v>
       </c>
-      <c r="J33" s="65" t="e">
+      <c r="J33" s="92" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A34" s="4">
+      <c r="A34" s="69">
         <f t="shared" ref="A34:A52" si="3">ROW()-1</f>
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="str">
+      <c r="B34" s="69" t="str">
         <f>_xlfn.XLOOKUP($C34,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C34" s="15" t="str">
+      <c r="C34" s="70" t="str">
         <f t="array" ref="C34">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E34)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D34" s="11" t="str">
+      <c r="D34" s="75" t="str">
         <f>_xlfn.XLOOKUP($C34,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E34" s="4"/>
-      <c r="F34" s="62"/>
-      <c r="G34" s="74">
-        <v>0</v>
-      </c>
-      <c r="H34" s="75">
+      <c r="E34" s="86"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="89">
+        <v>0</v>
+      </c>
+      <c r="H34" s="90">
         <v>3</v>
       </c>
-      <c r="I34" s="76">
+      <c r="I34" s="91">
         <f t="shared" ref="I34:I51" si="4">$I33+TIME(0,0,15)+$F34</f>
         <v>0.81822916666666756</v>
       </c>
-      <c r="J34" s="65" t="e">
+      <c r="J34" s="92" t="e">
         <f t="shared" ref="J34:J52" si="5">"ren """ &amp; E34 &amp; """ """ &amp; TEXT(ROW(A33),"00") &amp; "-" &amp; LEFT(E34,FIND(".",E34)-1) &amp; MID(E34,FIND(".",E34),LEN(E34)) &amp; """"</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A35" s="4">
+      <c r="A35" s="69">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="str">
+      <c r="B35" s="69" t="str">
         <f>_xlfn.XLOOKUP($C35,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C35" s="15" t="str">
+      <c r="C35" s="70" t="str">
         <f t="array" ref="C35">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E35)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D35" s="5" t="str">
+      <c r="D35" s="71" t="str">
         <f>_xlfn.XLOOKUP($C35,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="74">
-        <v>0</v>
-      </c>
-      <c r="H35" s="75">
+      <c r="E35" s="86"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="89">
+        <v>0</v>
+      </c>
+      <c r="H35" s="90">
         <v>3</v>
       </c>
-      <c r="I35" s="76">
+      <c r="I35" s="91">
         <f t="shared" si="4"/>
         <v>0.8184027777777787</v>
       </c>
-      <c r="J35" s="65" t="e">
+      <c r="J35" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="4">
+      <c r="A36" s="69">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="str">
+      <c r="B36" s="69" t="str">
         <f>_xlfn.XLOOKUP($C36,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C36" s="15" t="str">
+      <c r="C36" s="70" t="str">
         <f t="array" ref="C36">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E36)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D36" s="5" t="str">
+      <c r="D36" s="71" t="str">
         <f>_xlfn.XLOOKUP($C36,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="62"/>
-      <c r="G36" s="74">
-        <v>0</v>
-      </c>
-      <c r="H36" s="75">
+      <c r="E36" s="86"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="89">
+        <v>0</v>
+      </c>
+      <c r="H36" s="90">
         <v>3</v>
       </c>
-      <c r="I36" s="76">
+      <c r="I36" s="91">
         <f t="shared" si="4"/>
         <v>0.81857638888888984</v>
       </c>
-      <c r="J36" s="65" t="e">
+      <c r="J36" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A37" s="4">
+      <c r="A37" s="69">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="str">
+      <c r="B37" s="69" t="str">
         <f>_xlfn.XLOOKUP($C37,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C37" s="15" t="str">
+      <c r="C37" s="70" t="str">
         <f t="array" ref="C37">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E37)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D37" s="11" t="str">
+      <c r="D37" s="75" t="str">
         <f>_xlfn.XLOOKUP($C37,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E37" s="4"/>
-      <c r="F37" s="62"/>
-      <c r="G37" s="74">
-        <v>0</v>
-      </c>
-      <c r="H37" s="75">
+      <c r="E37" s="86"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="89">
+        <v>0</v>
+      </c>
+      <c r="H37" s="90">
         <v>3</v>
       </c>
-      <c r="I37" s="76">
+      <c r="I37" s="91">
         <f t="shared" si="4"/>
         <v>0.81875000000000098</v>
       </c>
-      <c r="J37" s="65" t="e">
+      <c r="J37" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A38" s="4">
+      <c r="A38" s="69">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="str">
+      <c r="B38" s="69" t="str">
         <f>_xlfn.XLOOKUP($C38,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C38" s="15" t="str">
+      <c r="C38" s="70" t="str">
         <f t="array" ref="C38">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E38)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D38" s="5" t="str">
+      <c r="D38" s="71" t="str">
         <f>_xlfn.XLOOKUP($C38,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="62"/>
-      <c r="G38" s="74">
-        <v>0</v>
-      </c>
-      <c r="H38" s="75">
+      <c r="E38" s="87"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="89">
+        <v>0</v>
+      </c>
+      <c r="H38" s="90">
         <v>3</v>
       </c>
-      <c r="I38" s="76">
+      <c r="I38" s="91">
         <f t="shared" si="4"/>
         <v>0.81892361111111212</v>
       </c>
-      <c r="J38" s="65" t="e">
+      <c r="J38" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A39" s="4">
+      <c r="A39" s="69">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="str">
+      <c r="B39" s="69" t="str">
         <f>_xlfn.XLOOKUP($C39,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C39" s="15" t="str">
+      <c r="C39" s="70" t="str">
         <f t="array" ref="C39">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E39)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D39" s="5" t="str">
+      <c r="D39" s="71" t="str">
         <f>_xlfn.XLOOKUP($C39,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E39" s="4"/>
-      <c r="F39" s="62"/>
-      <c r="G39" s="74">
-        <v>0</v>
-      </c>
-      <c r="H39" s="75">
+      <c r="E39" s="86"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="89">
+        <v>0</v>
+      </c>
+      <c r="H39" s="90">
         <v>3</v>
       </c>
-      <c r="I39" s="76">
+      <c r="I39" s="91">
         <f t="shared" si="4"/>
         <v>0.81909722222222325</v>
       </c>
-      <c r="J39" s="65" t="e">
+      <c r="J39" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A40" s="4">
+      <c r="A40" s="69">
         <f t="shared" si="3"/>
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="str">
+      <c r="B40" s="69" t="str">
         <f>_xlfn.XLOOKUP($C40,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C40" s="15" t="str">
+      <c r="C40" s="70" t="str">
         <f t="array" ref="C40">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E40)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D40" s="5" t="str">
+      <c r="D40" s="71" t="str">
         <f>_xlfn.XLOOKUP($C40,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E40" s="4"/>
-      <c r="F40" s="62"/>
-      <c r="G40" s="74">
-        <v>0</v>
-      </c>
-      <c r="H40" s="75">
+      <c r="E40" s="86"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="89">
+        <v>0</v>
+      </c>
+      <c r="H40" s="90">
         <v>3</v>
       </c>
-      <c r="I40" s="76">
+      <c r="I40" s="91">
         <f t="shared" si="4"/>
         <v>0.81927083333333439</v>
       </c>
-      <c r="J40" s="65" t="e">
+      <c r="J40" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A41" s="4">
+      <c r="A41" s="69">
         <f t="shared" si="3"/>
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="str">
+      <c r="B41" s="69" t="str">
         <f>_xlfn.XLOOKUP($C41,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C41" s="15" t="str">
+      <c r="C41" s="70" t="str">
         <f t="array" ref="C41">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E41)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D41" s="8" t="str">
+      <c r="D41" s="72" t="str">
         <f>_xlfn.XLOOKUP($C41,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E41" s="4"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="74">
-        <v>0</v>
-      </c>
-      <c r="H41" s="75">
+      <c r="E41" s="86"/>
+      <c r="F41" s="88"/>
+      <c r="G41" s="89">
+        <v>0</v>
+      </c>
+      <c r="H41" s="90">
         <v>3</v>
       </c>
-      <c r="I41" s="76">
+      <c r="I41" s="91">
         <f t="shared" si="4"/>
         <v>0.81944444444444553</v>
       </c>
-      <c r="J41" s="65" t="e">
+      <c r="J41" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A42" s="4">
+      <c r="A42" s="69">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="str">
+      <c r="B42" s="69" t="str">
         <f>_xlfn.XLOOKUP($C42,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C42" s="15" t="str">
+      <c r="C42" s="70" t="str">
         <f t="array" ref="C42">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E42)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D42" s="5" t="str">
+      <c r="D42" s="71" t="str">
         <f>_xlfn.XLOOKUP($C42,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="62"/>
-      <c r="G42" s="74">
-        <v>0</v>
-      </c>
-      <c r="H42" s="75">
+      <c r="E42" s="86"/>
+      <c r="F42" s="88"/>
+      <c r="G42" s="89">
+        <v>0</v>
+      </c>
+      <c r="H42" s="90">
         <v>3</v>
       </c>
-      <c r="I42" s="76">
+      <c r="I42" s="91">
         <f t="shared" si="4"/>
         <v>0.81961805555555667</v>
       </c>
-      <c r="J42" s="65" t="e">
+      <c r="J42" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A43" s="4">
+      <c r="A43" s="69">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="str">
+      <c r="B43" s="69" t="str">
         <f>_xlfn.XLOOKUP($C43,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C43" s="15" t="str">
+      <c r="C43" s="70" t="str">
         <f t="array" ref="C43">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E43)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D43" s="5" t="str">
+      <c r="D43" s="71" t="str">
         <f>_xlfn.XLOOKUP($C43,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="62"/>
-      <c r="G43" s="74">
-        <v>0</v>
-      </c>
-      <c r="H43" s="75">
+      <c r="E43" s="87"/>
+      <c r="F43" s="88"/>
+      <c r="G43" s="89">
+        <v>0</v>
+      </c>
+      <c r="H43" s="90">
         <v>3</v>
       </c>
-      <c r="I43" s="76">
+      <c r="I43" s="91">
         <f t="shared" si="4"/>
         <v>0.81979166666666781</v>
       </c>
-      <c r="J43" s="65" t="e">
+      <c r="J43" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A44" s="4">
+      <c r="A44" s="69">
         <f t="shared" si="3"/>
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="str">
+      <c r="B44" s="69" t="str">
         <f>_xlfn.XLOOKUP($C44,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C44" s="15" t="str">
+      <c r="C44" s="70" t="str">
         <f t="array" ref="C44">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E44)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D44" s="7" t="str">
+      <c r="D44" s="73" t="str">
         <f>_xlfn.XLOOKUP($C44,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="62"/>
-      <c r="G44" s="74">
-        <v>0</v>
-      </c>
-      <c r="H44" s="75">
+      <c r="E44" s="87"/>
+      <c r="F44" s="88"/>
+      <c r="G44" s="89">
+        <v>0</v>
+      </c>
+      <c r="H44" s="90">
         <v>3</v>
       </c>
-      <c r="I44" s="76">
+      <c r="I44" s="91">
         <f t="shared" si="4"/>
         <v>0.81996527777777894</v>
       </c>
-      <c r="J44" s="65" t="e">
+      <c r="J44" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A45" s="4">
+      <c r="A45" s="69">
         <f t="shared" si="3"/>
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="str">
+      <c r="B45" s="69" t="str">
         <f>_xlfn.XLOOKUP($C45,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C45" s="15" t="str">
+      <c r="C45" s="70" t="str">
         <f t="array" ref="C45">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E45)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D45" s="7" t="str">
+      <c r="D45" s="73" t="str">
         <f>_xlfn.XLOOKUP($C45,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="62"/>
-      <c r="G45" s="74">
-        <v>0</v>
-      </c>
-      <c r="H45" s="75">
+      <c r="E45" s="87"/>
+      <c r="F45" s="88"/>
+      <c r="G45" s="89">
+        <v>0</v>
+      </c>
+      <c r="H45" s="90">
         <v>3</v>
       </c>
-      <c r="I45" s="76">
+      <c r="I45" s="91">
         <f t="shared" si="4"/>
         <v>0.82013888888889008</v>
       </c>
-      <c r="J45" s="65" t="e">
+      <c r="J45" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A46" s="4">
+      <c r="A46" s="69">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="str">
+      <c r="B46" s="69" t="str">
         <f>_xlfn.XLOOKUP($C46,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C46" s="15" t="str">
+      <c r="C46" s="70" t="str">
         <f t="array" ref="C46">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E46)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D46" s="5" t="str">
+      <c r="D46" s="71" t="str">
         <f>_xlfn.XLOOKUP($C46,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="62"/>
-      <c r="G46" s="74">
-        <v>0</v>
-      </c>
-      <c r="H46" s="75">
+      <c r="E46" s="86"/>
+      <c r="F46" s="88"/>
+      <c r="G46" s="89">
+        <v>0</v>
+      </c>
+      <c r="H46" s="90">
         <v>3</v>
       </c>
-      <c r="I46" s="76">
+      <c r="I46" s="91">
         <f t="shared" si="4"/>
         <v>0.82031250000000122</v>
       </c>
-      <c r="J46" s="65" t="e">
+      <c r="J46" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A47" s="4">
+      <c r="A47" s="69">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="str">
+      <c r="B47" s="69" t="str">
         <f>_xlfn.XLOOKUP($C47,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C47" s="15" t="str">
+      <c r="C47" s="70" t="str">
         <f t="array" ref="C47">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E47)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D47" s="5" t="str">
+      <c r="D47" s="71" t="str">
         <f>_xlfn.XLOOKUP($C47,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="62"/>
-      <c r="G47" s="74">
-        <v>0</v>
-      </c>
-      <c r="H47" s="75">
+      <c r="E47" s="86"/>
+      <c r="F47" s="88"/>
+      <c r="G47" s="89">
+        <v>0</v>
+      </c>
+      <c r="H47" s="90">
         <v>3</v>
       </c>
-      <c r="I47" s="76">
+      <c r="I47" s="91">
         <f t="shared" si="4"/>
         <v>0.82048611111111236</v>
       </c>
-      <c r="J47" s="65" t="e">
+      <c r="J47" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A48" s="4">
+      <c r="A48" s="69">
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="str">
+      <c r="B48" s="69" t="str">
         <f>_xlfn.XLOOKUP($C48,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C48" s="15" t="str">
+      <c r="C48" s="70" t="str">
         <f t="array" ref="C48">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E48)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D48" s="5" t="str">
+      <c r="D48" s="71" t="str">
         <f>_xlfn.XLOOKUP($C48,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="62"/>
-      <c r="G48" s="74">
-        <v>0</v>
-      </c>
-      <c r="H48" s="75">
+      <c r="E48" s="87"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="89">
+        <v>0</v>
+      </c>
+      <c r="H48" s="90">
         <v>3</v>
       </c>
-      <c r="I48" s="76">
+      <c r="I48" s="91">
         <f t="shared" si="4"/>
         <v>0.8206597222222235</v>
       </c>
-      <c r="J48" s="65" t="e">
+      <c r="J48" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A49" s="4">
+      <c r="A49" s="69">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="str">
+      <c r="B49" s="69" t="str">
         <f>_xlfn.XLOOKUP($C49,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C49" s="15" t="str">
+      <c r="C49" s="70" t="str">
         <f t="array" ref="C49">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E49)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D49" s="5" t="str">
+      <c r="D49" s="71" t="str">
         <f>_xlfn.XLOOKUP($C49,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="62"/>
-      <c r="G49" s="74">
-        <v>0</v>
-      </c>
-      <c r="H49" s="75">
+      <c r="E49" s="87"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="89">
+        <v>0</v>
+      </c>
+      <c r="H49" s="90">
         <v>3</v>
       </c>
-      <c r="I49" s="76">
+      <c r="I49" s="91">
         <f t="shared" si="4"/>
         <v>0.82083333333333464</v>
       </c>
-      <c r="J49" s="65" t="e">
+      <c r="J49" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A50" s="4">
+      <c r="A50" s="69">
         <f t="shared" si="3"/>
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="str">
+      <c r="B50" s="69" t="str">
         <f>_xlfn.XLOOKUP($C50,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C50" s="15" t="str">
+      <c r="C50" s="70" t="str">
         <f t="array" ref="C50">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E50)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D50" s="8" t="str">
+      <c r="D50" s="72" t="str">
         <f>_xlfn.XLOOKUP($C50,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="62"/>
-      <c r="G50" s="74">
-        <v>0</v>
-      </c>
-      <c r="H50" s="75">
+      <c r="E50" s="94"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="89">
+        <v>0</v>
+      </c>
+      <c r="H50" s="90">
         <v>3</v>
       </c>
-      <c r="I50" s="76">
+      <c r="I50" s="91">
         <f t="shared" si="4"/>
         <v>0.82100694444444577</v>
       </c>
-      <c r="J50" s="65" t="e">
+      <c r="J50" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A51" s="4">
+      <c r="A51" s="69">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="str">
+      <c r="B51" s="69" t="str">
         <f>_xlfn.XLOOKUP($C51,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C51" s="15" t="str">
+      <c r="C51" s="70" t="str">
         <f t="array" ref="C51">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E51)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D51" s="8" t="str">
+      <c r="D51" s="72" t="str">
         <f>_xlfn.XLOOKUP($C51,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="62"/>
-      <c r="G51" s="74">
-        <v>0</v>
-      </c>
-      <c r="H51" s="75">
+      <c r="E51" s="93"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="89">
+        <v>0</v>
+      </c>
+      <c r="H51" s="90">
         <v>3</v>
       </c>
-      <c r="I51" s="76">
+      <c r="I51" s="91">
         <f t="shared" si="4"/>
         <v>0.82118055555555691</v>
       </c>
-      <c r="J51" s="65" t="e">
+      <c r="J51" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A52" s="4">
+      <c r="A52" s="69">
         <f t="shared" si="3"/>
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="str">
+      <c r="B52" s="69" t="str">
         <f>_xlfn.XLOOKUP($C52,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C52" s="15" t="str">
+      <c r="C52" s="70" t="str">
         <f t="array" ref="C52">_xlfn.LET(
    _xlpm.keywords, _xlfn.SORTBY(舞种配比!$B$2:$B$50, LEN(舞种配比!$B$2:$B$50), -1),
    _xlfn.XLOOKUP(TRUE, ISNUMBER(SEARCH(_xlpm.keywords, E52)), _xlpm.keywords, "")
 )</f>
         <v/>
       </c>
-      <c r="D52" s="5" t="str">
+      <c r="D52" s="71" t="str">
         <f>_xlfn.XLOOKUP($C52,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="74">
-        <v>0</v>
-      </c>
-      <c r="H52" s="75"/>
-      <c r="J52" s="65" t="e">
+      <c r="E52" s="87"/>
+      <c r="F52" s="95"/>
+      <c r="G52" s="89">
+        <v>0</v>
+      </c>
+      <c r="H52" s="90"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="92" t="e">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="63"/>
-      <c r="B53" s="63" t="str">
+      <c r="A53" s="77"/>
+      <c r="B53" s="77" t="str">
         <f>_xlfn.XLOOKUP($C53,舞种配比!$B$2:$B$91,舞种配比!$A$2:$A$91,"")</f>
         <v/>
       </c>
-      <c r="C53" s="64" t="s">
+      <c r="C53" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="D53" s="64" t="str">
+      <c r="D53" s="78" t="str">
         <f>_xlfn.XLOOKUP($C53,舞种配比!$B$2:$B$91,舞种配比!$C$2:$C$91,"")</f>
         <v/>
       </c>
-      <c r="E53" s="66"/>
-      <c r="F53" s="68">
+      <c r="E53" s="97"/>
+      <c r="F53" s="98">
         <f>SUM(F2:F52)</f>
         <v>0</v>
       </c>
-      <c r="G53" s="69">
+      <c r="G53" s="99">
         <f>COUNTA(E:E)-1</f>
         <v>0</v>
       </c>
-      <c r="H53" s="70" t="str">
+      <c r="H53" s="100" t="str">
         <f t="array" ref="H53">_xlfn.LET(
     _xlpm.总分钟, SUMPRODUCT((H2:H52&lt;&gt;"") * H2:H52 + (H2:H52="") * (HOUR(F2:F52)*60 + MINUTE(F2:F52) + SECOND(F2:F52)/60)),
     _xlpm.小时, INT(_xlpm.总分钟/60),
@@ -7478,19 +7604,25 @@
 )</f>
         <v>2小时30分钟</v>
       </c>
+      <c r="I53" s="96"/>
+      <c r="J53" s="101"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="F54" s="71" t="s">
+      <c r="E54" s="102"/>
+      <c r="F54" s="103" t="s">
         <v>189</v>
       </c>
-      <c r="G54" s="72" t="s">
+      <c r="G54" s="104" t="s">
         <v>190</v>
       </c>
-      <c r="H54" s="72" t="s">
+      <c r="H54" s="104" t="s">
         <v>191</v>
       </c>
+      <c r="I54" s="96"/>
+      <c r="J54" s="101"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:H52">
     <cfRule type="expression" dxfId="11" priority="4">
